--- a/jogos_2026-06-24.xlsx
+++ b/jogos_2026-06-24.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2026-06-24.xlsx
+++ b/jogos_2026-06-24.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G7" t="n">

--- a/jogos_2026-06-24.xlsx
+++ b/jogos_2026-06-24.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2026-06-24.xlsx
+++ b/jogos_2026-06-24.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2026-06-24.xlsx
+++ b/jogos_2026-06-24.xlsx
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G7" t="n">

--- a/jogos_2026-06-24.xlsx
+++ b/jogos_2026-06-24.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G7" t="n">

--- a/jogos_2026-06-24.xlsx
+++ b/jogos_2026-06-24.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G6" t="n">

--- a/jogos_2026-06-24.xlsx
+++ b/jogos_2026-06-24.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G4" t="n">

--- a/jogos_2026-06-24.xlsx
+++ b/jogos_2026-06-24.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2026-06-24.xlsx
+++ b/jogos_2026-06-24.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2026-06-24.xlsx
+++ b/jogos_2026-06-24.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2026-06-24.xlsx
+++ b/jogos_2026-06-24.xlsx
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G6" t="n">

--- a/jogos_2026-06-24.xlsx
+++ b/jogos_2026-06-24.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G7" t="n">

--- a/jogos_2026-06-24.xlsx
+++ b/jogos_2026-06-24.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="G7" t="n">

--- a/jogos_2026-06-24.xlsx
+++ b/jogos_2026-06-24.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2026-06-24.xlsx
+++ b/jogos_2026-06-24.xlsx
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2026-06-24.xlsx
+++ b/jogos_2026-06-24.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2026-06-24.xlsx
+++ b/jogos_2026-06-24.xlsx
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="G6" t="n">

--- a/jogos_2026-06-24.xlsx
+++ b/jogos_2026-06-24.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2026-06-24.xlsx
+++ b/jogos_2026-06-24.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2026-06-24.xlsx
+++ b/jogos_2026-06-24.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G6" t="n">

--- a/jogos_2026-06-24.xlsx
+++ b/jogos_2026-06-24.xlsx
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G7" t="n">

--- a/jogos_2026-06-24.xlsx
+++ b/jogos_2026-06-24.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2026-06-24.xlsx
+++ b/jogos_2026-06-24.xlsx
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2026-06-24.xlsx
+++ b/jogos_2026-06-24.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G4" t="n">

--- a/jogos_2026-06-24.xlsx
+++ b/jogos_2026-06-24.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2026-06-24.xlsx
+++ b/jogos_2026-06-24.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G7" t="n">

--- a/jogos_2026-06-24.xlsx
+++ b/jogos_2026-06-24.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G3" t="n">

--- a/jogos_2026-06-24.xlsx
+++ b/jogos_2026-06-24.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G7" t="n">

--- a/jogos_2026-06-24.xlsx
+++ b/jogos_2026-06-24.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G3" t="n">

--- a/jogos_2026-06-24.xlsx
+++ b/jogos_2026-06-24.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="G7" t="n">

--- a/jogos_2026-06-24.xlsx
+++ b/jogos_2026-06-24.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G7" t="n">

--- a/jogos_2026-06-24.xlsx
+++ b/jogos_2026-06-24.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2026-06-24.xlsx
+++ b/jogos_2026-06-24.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>4.62</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>

--- a/jogos_2026-06-24.xlsx
+++ b/jogos_2026-06-24.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G6" t="n">

--- a/jogos_2026-06-24.xlsx
+++ b/jogos_2026-06-24.xlsx
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G7" t="n">

--- a/jogos_2026-06-24.xlsx
+++ b/jogos_2026-06-24.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="G7" t="n">

--- a/jogos_2026-06-24.xlsx
+++ b/jogos_2026-06-24.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>

--- a/jogos_2026-06-24.xlsx
+++ b/jogos_2026-06-24.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,19 +725,19 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -746,10 +746,10 @@
         <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
@@ -758,31 +758,31 @@
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -893,10 +893,10 @@
         <v>1.11</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -905,10 +905,10 @@
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
@@ -917,31 +917,31 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,19 +1202,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.14</v>
+        <v>1.75</v>
       </c>
       <c r="O5" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P5" t="n">
-        <v>2.89</v>
+        <v>4.04</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1223,10 +1223,10 @@
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
@@ -1235,31 +1235,31 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,19 +1361,19 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="O6" t="n">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="P6" t="n">
-        <v>4.04</v>
+        <v>3.45</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1382,10 +1382,10 @@
         <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
@@ -1394,31 +1394,31 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,19 +1520,19 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.95</v>
+        <v>2.14</v>
       </c>
       <c r="O7" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="P7" t="n">
-        <v>3.45</v>
+        <v>2.89</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1541,10 +1541,10 @@
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
@@ -1553,25 +1553,25 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF7" t="n">
         <v>0</v>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="O8" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="P8" t="n">
+        <v>6.32</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="R8" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AD8" t="n">
         <v>1.47</v>
       </c>
-      <c r="O8" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="P8" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" t="n">
-        <v>0</v>
-      </c>
-      <c r="W8" t="n">
-        <v>0</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>0</v>
-      </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.8</v>
+        <v>2.53</v>
       </c>
       <c r="O9" t="n">
-        <v>3.4</v>
+        <v>3.28</v>
       </c>
       <c r="P9" t="n">
-        <v>2.2</v>
+        <v>2.44</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="O10" t="n">
-        <v>3.68</v>
+        <v>3.72</v>
       </c>
       <c r="P10" t="n">
-        <v>4.62</v>
+        <v>4.77</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>

--- a/jogos_2026-06-24.xlsx
+++ b/jogos_2026-06-24.xlsx
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,19 +884,19 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -905,10 +905,10 @@
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
@@ -917,31 +917,31 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,19 +1043,19 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1064,10 +1064,10 @@
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
@@ -1076,31 +1076,31 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.75</v>
+        <v>2.14</v>
       </c>
       <c r="O5" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P5" t="n">
-        <v>4.04</v>
+        <v>2.89</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.23</v>
+        <v>2.55</v>
       </c>
       <c r="R5" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AB5" t="n">
         <v>2.38</v>
       </c>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AC5" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.43</v>
+        <v>1.55</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.87</v>
+        <v>1.55</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,19 +1520,19 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.14</v>
+        <v>1.75</v>
       </c>
       <c r="O7" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P7" t="n">
-        <v>2.89</v>
+        <v>4.04</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.55</v>
+        <v>2.23</v>
       </c>
       <c r="R7" t="n">
-        <v>2.43</v>
+        <v>2.38</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1541,43 +1541,43 @@
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>2.08</v>
+        <v>2.28</v>
       </c>
       <c r="V7" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AF7" t="n">
         <v>1.58</v>
       </c>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>0</v>
-      </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.55</v>
+        <v>1.87</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.42</v>
+        <v>2.53</v>
       </c>
       <c r="O8" t="n">
-        <v>4.6</v>
+        <v>3.28</v>
       </c>
       <c r="P8" t="n">
-        <v>6.32</v>
+        <v>2.44</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.91</v>
+        <v>3.18</v>
       </c>
       <c r="R8" t="n">
-        <v>2.38</v>
+        <v>2.12</v>
       </c>
       <c r="S8" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="T8" t="n">
-        <v>3.25</v>
+        <v>2.91</v>
       </c>
       <c r="U8" t="n">
-        <v>2.28</v>
+        <v>2.59</v>
       </c>
       <c r="V8" t="n">
-        <v>1.55</v>
+        <v>1.41</v>
       </c>
       <c r="W8" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="X8" t="n">
         <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.45</v>
+        <v>3.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.25</v>
+        <v>1.9</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.35</v>
+        <v>3.03</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.78</v>
+        <v>1.63</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.91</v>
+        <v>2.12</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.06</v>
+        <v>1.5</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.57</v>
+        <v>1.4</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.53</v>
+        <v>1.42</v>
       </c>
       <c r="O9" t="n">
-        <v>3.28</v>
+        <v>4.6</v>
       </c>
       <c r="P9" t="n">
-        <v>2.44</v>
+        <v>6.32</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.18</v>
+        <v>1.91</v>
       </c>
       <c r="R9" t="n">
-        <v>2.12</v>
+        <v>2.38</v>
       </c>
       <c r="S9" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="T9" t="n">
-        <v>2.91</v>
+        <v>3.25</v>
       </c>
       <c r="U9" t="n">
-        <v>2.59</v>
+        <v>2.28</v>
       </c>
       <c r="V9" t="n">
-        <v>1.41</v>
+        <v>1.55</v>
       </c>
       <c r="W9" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="X9" t="n">
         <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.5</v>
+        <v>4.45</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.9</v>
+        <v>2.25</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.03</v>
+        <v>2.35</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.12</v>
+        <v>1.91</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.5</v>
+        <v>1.06</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.4</v>
+        <v>2.57</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>

--- a/jogos_2026-06-24.xlsx
+++ b/jogos_2026-06-24.xlsx
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,19 +884,19 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -905,10 +905,10 @@
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
@@ -917,31 +917,31 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,19 +1043,19 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1064,10 +1064,10 @@
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
@@ -1076,31 +1076,31 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,19 +1202,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.14</v>
+        <v>1.75</v>
       </c>
       <c r="O5" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P5" t="n">
-        <v>2.89</v>
+        <v>4.04</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.55</v>
+        <v>2.23</v>
       </c>
       <c r="R5" t="n">
-        <v>2.43</v>
+        <v>2.38</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1223,43 +1223,43 @@
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>2.08</v>
+        <v>2.28</v>
       </c>
       <c r="V5" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AF5" t="n">
         <v>1.58</v>
       </c>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>0</v>
-      </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.55</v>
+        <v>1.87</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,20 +1361,20 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.95</v>
+        <v>2.14</v>
       </c>
       <c r="O6" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="P6" t="n">
-        <v>3.45</v>
+        <v>2.89</v>
       </c>
       <c r="Q6" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="R6" t="n">
         <v>2.43</v>
       </c>
-      <c r="R6" t="n">
-        <v>2.3</v>
-      </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
@@ -1382,10 +1382,10 @@
         <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>2.33</v>
+        <v>2.08</v>
       </c>
       <c r="V6" t="n">
-        <v>1.47</v>
+        <v>1.58</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
@@ -1394,31 +1394,31 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.9</v>
+        <v>4.7</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.64</v>
+        <v>1.48</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.04</v>
+        <v>2.38</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.68</v>
+        <v>1.55</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,19 +1520,19 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="O7" t="n">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="P7" t="n">
-        <v>4.04</v>
+        <v>3.45</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.23</v>
+        <v>2.43</v>
       </c>
       <c r="R7" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1541,10 +1541,10 @@
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>2.28</v>
+        <v>2.33</v>
       </c>
       <c r="V7" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
@@ -1553,31 +1553,31 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="Z7" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.87</v>
+        <v>1.68</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1700,34 +1700,34 @@
         <v>2.91</v>
       </c>
       <c r="U8" t="n">
-        <v>2.59</v>
+        <v>2.5</v>
       </c>
       <c r="V8" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="W8" t="n">
         <v>1.06</v>
       </c>
       <c r="X8" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z8" t="n">
         <v>3.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AC8" t="n">
         <v>3.03</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AE8" t="n">
         <v>1.13</v>
@@ -1736,7 +1736,7 @@
         <v>1.63</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.12</v>
+        <v>2.07</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,7 +1749,7 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="AK8" t="n">
         <v>1.4</v>
@@ -1838,10 +1838,10 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="O9" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="P9" t="n">
         <v>6.32</v>
@@ -1856,10 +1856,10 @@
         <v>1.27</v>
       </c>
       <c r="T9" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="U9" t="n">
-        <v>2.28</v>
+        <v>2.37</v>
       </c>
       <c r="V9" t="n">
         <v>1.55</v>
@@ -1880,7 +1880,7 @@
         <v>1.57</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AC9" t="n">
         <v>2.35</v>
@@ -1895,7 +1895,7 @@
         <v>1.78</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="AK9" t="n">
         <v>2.57</v>
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="O10" t="n">
-        <v>3.72</v>
+        <v>3.65</v>
       </c>
       <c r="P10" t="n">
-        <v>4.77</v>
+        <v>4.47</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>

--- a/jogos_2026-06-24.xlsx
+++ b/jogos_2026-06-24.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,19 +725,19 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.34</v>
+        <v>15</v>
       </c>
       <c r="O2" t="n">
-        <v>3.4</v>
+        <v>7.6</v>
       </c>
       <c r="P2" t="n">
-        <v>2.65</v>
+        <v>1.11</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.8</v>
+        <v>10</v>
       </c>
       <c r="R2" t="n">
-        <v>2.3</v>
+        <v>3.3</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -746,10 +746,10 @@
         <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>2.25</v>
+        <v>1.84</v>
       </c>
       <c r="V2" t="n">
-        <v>1.49</v>
+        <v>1.76</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
@@ -758,31 +758,31 @@
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="Z2" t="n">
-        <v>4</v>
+        <v>5.75</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.61</v>
+        <v>1.33</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.08</v>
+        <v>2.88</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.55</v>
+        <v>1.86</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.42</v>
+        <v>1.79</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.15</v>
+        <v>1.33</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.5</v>
+        <v>2.05</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.3</v>
+        <v>1.64</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.22</v>
+        <v>1.05</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.45</v>
+        <v>1.01</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,19 +884,19 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>15</v>
+        <v>2.34</v>
       </c>
       <c r="O3" t="n">
-        <v>7.6</v>
+        <v>3.4</v>
       </c>
       <c r="P3" t="n">
-        <v>1.11</v>
+        <v>2.65</v>
       </c>
       <c r="Q3" t="n">
-        <v>10</v>
+        <v>2.8</v>
       </c>
       <c r="R3" t="n">
-        <v>3.3</v>
+        <v>2.3</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -905,10 +905,10 @@
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1.84</v>
+        <v>2.25</v>
       </c>
       <c r="V3" t="n">
-        <v>1.76</v>
+        <v>1.49</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
@@ -917,31 +917,31 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="Z3" t="n">
-        <v>5.75</v>
+        <v>4</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.33</v>
+        <v>1.61</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.88</v>
+        <v>2.08</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.86</v>
+        <v>2.55</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.79</v>
+        <v>1.42</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.33</v>
+        <v>1.15</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.05</v>
+        <v>1.5</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.64</v>
+        <v>2.3</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.05</v>
+        <v>1.22</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.75</v>
+        <v>2.14</v>
       </c>
       <c r="O5" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P5" t="n">
-        <v>4.04</v>
+        <v>2.89</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.23</v>
+        <v>2.55</v>
       </c>
       <c r="R5" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AB5" t="n">
         <v>2.38</v>
       </c>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AC5" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.43</v>
+        <v>1.55</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.87</v>
+        <v>1.55</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,19 +1361,19 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.14</v>
+        <v>1.75</v>
       </c>
       <c r="O6" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P6" t="n">
-        <v>2.89</v>
+        <v>4.04</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.55</v>
+        <v>2.23</v>
       </c>
       <c r="R6" t="n">
-        <v>2.43</v>
+        <v>2.38</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1382,43 +1382,43 @@
         <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>2.08</v>
+        <v>2.28</v>
       </c>
       <c r="V6" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AF6" t="n">
         <v>1.58</v>
       </c>
-      <c r="W6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>0</v>
-      </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.55</v>
+        <v>1.87</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,80 +1679,80 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.53</v>
+        <v>1.4</v>
       </c>
       <c r="O8" t="n">
-        <v>3.28</v>
+        <v>4.4</v>
       </c>
       <c r="P8" t="n">
-        <v>2.44</v>
+        <v>6.32</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.18</v>
+        <v>1.91</v>
       </c>
       <c r="R8" t="n">
-        <v>2.12</v>
+        <v>2.38</v>
       </c>
       <c r="S8" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="T8" t="n">
-        <v>2.91</v>
+        <v>3.5</v>
       </c>
       <c r="U8" t="n">
-        <v>2.5</v>
+        <v>2.37</v>
       </c>
       <c r="V8" t="n">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="W8" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.5</v>
+        <v>4.45</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.03</v>
+        <v>2.35</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.3</v>
+        <v>1.47</v>
       </c>
       <c r="AE8" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ8" t="n">
         <v>1.13</v>
       </c>
-      <c r="AF8" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AK8" t="n">
-        <v>1.4</v>
+        <v>2.57</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,80 +1838,80 @@
         </is>
       </c>
       <c r="N9" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="O9" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="R9" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AK9" t="n">
         <v>1.4</v>
-      </c>
-      <c r="O9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="P9" t="n">
-        <v>6.32</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="R9" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="S9" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="T9" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U9" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>2.57</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>

--- a/jogos_2026-06-24.xlsx
+++ b/jogos_2026-06-24.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,19 +725,19 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -746,10 +746,10 @@
         <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
@@ -758,31 +758,31 @@
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -896,46 +896,46 @@
         <v>2.8</v>
       </c>
       <c r="R3" t="n">
-        <v>2.3</v>
+        <v>2.19</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U3" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="V3" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="Z3" t="n">
-        <v>4</v>
+        <v>4.15</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.55</v>
+        <v>2.59</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AF3" t="n">
         <v>1.5</v>
@@ -957,7 +957,7 @@
         <v>1.22</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,19 +1043,19 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1064,10 +1064,10 @@
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
@@ -1076,31 +1076,31 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,19 +1361,19 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="O6" t="n">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="P6" t="n">
-        <v>4.04</v>
+        <v>3.45</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.23</v>
+        <v>2.43</v>
       </c>
       <c r="R6" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1382,10 +1382,10 @@
         <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>2.28</v>
+        <v>2.33</v>
       </c>
       <c r="V6" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
@@ -1394,31 +1394,31 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="Z6" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.87</v>
+        <v>1.68</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,19 +1520,19 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="O7" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="P7" t="n">
-        <v>3.45</v>
+        <v>4.04</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.43</v>
+        <v>2.23</v>
       </c>
       <c r="R7" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1541,10 +1541,10 @@
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>2.33</v>
+        <v>2.28</v>
       </c>
       <c r="V7" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
@@ -1553,31 +1553,31 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.68</v>
+        <v>1.87</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1691,19 +1691,19 @@
         <v>1.91</v>
       </c>
       <c r="R8" t="n">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="S8" t="n">
         <v>1.27</v>
       </c>
       <c r="T8" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="U8" t="n">
-        <v>2.37</v>
+        <v>2.29</v>
       </c>
       <c r="V8" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="W8" t="n">
         <v>1.09</v>
@@ -1736,7 +1736,7 @@
         <v>1.78</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.98</v>
+        <v>1.91</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1853,16 +1853,16 @@
         <v>2.12</v>
       </c>
       <c r="S9" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T9" t="n">
         <v>2.91</v>
       </c>
       <c r="U9" t="n">
-        <v>2.5</v>
+        <v>2.59</v>
       </c>
       <c r="V9" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="W9" t="n">
         <v>1.06</v>
@@ -1871,7 +1871,7 @@
         <v>1</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z9" t="n">
         <v>3.5</v>
@@ -1883,19 +1883,19 @@
         <v>1.95</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.03</v>
+        <v>2.92</v>
       </c>
       <c r="AD9" t="n">
         <v>1.3</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AF9" t="n">
         <v>1.63</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>

--- a/jogos_2026-06-24.xlsx
+++ b/jogos_2026-06-24.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,19 +725,19 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -746,10 +746,10 @@
         <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
@@ -758,31 +758,31 @@
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,19 +1043,19 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1064,10 +1064,10 @@
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
@@ -1076,31 +1076,31 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>

--- a/jogos_2026-06-24.xlsx
+++ b/jogos_2026-06-24.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,19 +725,19 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -746,10 +746,10 @@
         <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
@@ -758,31 +758,31 @@
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,65 +884,65 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.34</v>
+        <v>15</v>
       </c>
       <c r="O3" t="n">
-        <v>3.4</v>
+        <v>7.6</v>
       </c>
       <c r="P3" t="n">
-        <v>2.65</v>
+        <v>1.11</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.8</v>
+        <v>10</v>
       </c>
       <c r="R3" t="n">
-        <v>2.19</v>
+        <v>3.3</v>
       </c>
       <c r="S3" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>2.4</v>
+        <v>1.84</v>
       </c>
       <c r="V3" t="n">
-        <v>1.5</v>
+        <v>1.76</v>
       </c>
       <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
         <v>1.08</v>
       </c>
-      <c r="X3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.16</v>
-      </c>
       <c r="Z3" t="n">
-        <v>4.15</v>
+        <v>5.75</v>
       </c>
       <c r="AA3" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AG3" t="n">
         <v>1.64</v>
       </c>
-      <c r="AB3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>2.3</v>
-      </c>
       <c r="AH3" t="inlineStr">
         <is>
           <t>[]</t>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.22</v>
+        <v>1.05</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.48</v>
+        <v>1.01</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,19 +1361,19 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="O6" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="P6" t="n">
-        <v>3.45</v>
+        <v>4.04</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.43</v>
+        <v>2.23</v>
       </c>
       <c r="R6" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1382,10 +1382,10 @@
         <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>2.33</v>
+        <v>2.28</v>
       </c>
       <c r="V6" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
@@ -1394,31 +1394,31 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.68</v>
+        <v>1.87</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,19 +1520,19 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="O7" t="n">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="P7" t="n">
-        <v>4.04</v>
+        <v>3.45</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.23</v>
+        <v>2.43</v>
       </c>
       <c r="R7" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1541,10 +1541,10 @@
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>2.28</v>
+        <v>2.33</v>
       </c>
       <c r="V7" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
@@ -1553,31 +1553,31 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="Z7" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.87</v>
+        <v>1.68</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>

--- a/jogos_2026-06-24.xlsx
+++ b/jogos_2026-06-24.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,64 +725,64 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,19 +884,19 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -905,10 +905,10 @@
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
@@ -917,31 +917,31 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,65 +1043,65 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.34</v>
+        <v>15</v>
       </c>
       <c r="O4" t="n">
-        <v>3.4</v>
+        <v>7.6</v>
       </c>
       <c r="P4" t="n">
-        <v>2.65</v>
+        <v>1.11</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.8</v>
+        <v>10</v>
       </c>
       <c r="R4" t="n">
-        <v>2.19</v>
+        <v>3.3</v>
       </c>
       <c r="S4" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>2.4</v>
+        <v>1.84</v>
       </c>
       <c r="V4" t="n">
-        <v>1.5</v>
+        <v>1.76</v>
       </c>
       <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
         <v>1.08</v>
       </c>
-      <c r="X4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.16</v>
-      </c>
       <c r="Z4" t="n">
-        <v>4.15</v>
+        <v>5.75</v>
       </c>
       <c r="AA4" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AG4" t="n">
         <v>1.64</v>
       </c>
-      <c r="AB4" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>2.3</v>
-      </c>
       <c r="AH4" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.22</v>
+        <v>1.05</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.48</v>
+        <v>1.01</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,19 +1202,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.14</v>
+        <v>1.75</v>
       </c>
       <c r="O5" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P5" t="n">
-        <v>2.89</v>
+        <v>4.04</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.55</v>
+        <v>2.23</v>
       </c>
       <c r="R5" t="n">
-        <v>2.43</v>
+        <v>2.38</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1223,43 +1223,43 @@
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>2.08</v>
+        <v>2.28</v>
       </c>
       <c r="V5" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AF5" t="n">
         <v>1.58</v>
       </c>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>0</v>
-      </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.55</v>
+        <v>1.87</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,19 +1361,19 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="O6" t="n">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="P6" t="n">
-        <v>4.04</v>
+        <v>3.45</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.23</v>
+        <v>2.43</v>
       </c>
       <c r="R6" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1382,10 +1382,10 @@
         <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>2.28</v>
+        <v>2.33</v>
       </c>
       <c r="V6" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
@@ -1394,31 +1394,31 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="Z6" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.87</v>
+        <v>1.68</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,20 +1520,20 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.95</v>
+        <v>2.14</v>
       </c>
       <c r="O7" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="P7" t="n">
-        <v>3.45</v>
+        <v>2.89</v>
       </c>
       <c r="Q7" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="R7" t="n">
         <v>2.43</v>
       </c>
-      <c r="R7" t="n">
-        <v>2.3</v>
-      </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
@@ -1541,10 +1541,10 @@
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>2.33</v>
+        <v>2.08</v>
       </c>
       <c r="V7" t="n">
-        <v>1.47</v>
+        <v>1.58</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
@@ -1553,31 +1553,31 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.9</v>
+        <v>4.7</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.64</v>
+        <v>1.48</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.04</v>
+        <v>2.38</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.68</v>
+        <v>1.55</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,80 +1679,80 @@
         </is>
       </c>
       <c r="N8" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="O8" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="R8" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AK8" t="n">
         <v>1.4</v>
-      </c>
-      <c r="O8" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="P8" t="n">
-        <v>6.32</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="R8" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="S8" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="T8" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U8" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>2.57</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.53</v>
+        <v>1.4</v>
       </c>
       <c r="O9" t="n">
-        <v>3.28</v>
+        <v>4.4</v>
       </c>
       <c r="P9" t="n">
-        <v>2.44</v>
+        <v>6.32</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.18</v>
+        <v>1.91</v>
       </c>
       <c r="R9" t="n">
-        <v>2.12</v>
+        <v>2.43</v>
       </c>
       <c r="S9" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="T9" t="n">
-        <v>2.91</v>
+        <v>3.25</v>
       </c>
       <c r="U9" t="n">
-        <v>2.59</v>
+        <v>2.29</v>
       </c>
       <c r="V9" t="n">
-        <v>1.41</v>
+        <v>1.52</v>
       </c>
       <c r="W9" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.5</v>
+        <v>4.45</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.92</v>
+        <v>2.35</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.3</v>
+        <v>1.47</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.09</v>
+        <v>1.16</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.09</v>
+        <v>1.91</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.4</v>
+        <v>2.57</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>

--- a/jogos_2026-06-24.xlsx
+++ b/jogos_2026-06-24.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,64 +725,64 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>15</v>
+        <v>2.3</v>
       </c>
       <c r="O4" t="n">
-        <v>7.6</v>
+        <v>3.46</v>
       </c>
       <c r="P4" t="n">
-        <v>1.11</v>
+        <v>2.57</v>
       </c>
       <c r="Q4" t="n">
-        <v>10</v>
+        <v>2.88</v>
       </c>
       <c r="R4" t="n">
-        <v>3.3</v>
+        <v>2.3</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U4" t="n">
-        <v>1.84</v>
+        <v>2.41</v>
       </c>
       <c r="V4" t="n">
-        <v>1.76</v>
+        <v>1.46</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="Z4" t="n">
-        <v>5.75</v>
+        <v>4.15</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.33</v>
+        <v>1.61</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.88</v>
+        <v>2.08</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.86</v>
+        <v>2.55</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.79</v>
+        <v>1.42</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.33</v>
+        <v>1.15</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.05</v>
+        <v>1.5</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.64</v>
+        <v>2.3</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.05</v>
+        <v>1.39</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.75</v>
+        <v>2.14</v>
       </c>
       <c r="O5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="R5" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="T5" t="n">
         <v>3.7</v>
       </c>
-      <c r="P5" t="n">
-        <v>4.04</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="R5" t="n">
+      <c r="U5" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AB5" t="n">
         <v>2.38</v>
       </c>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AC5" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.43</v>
+        <v>1.55</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.58</v>
+        <v>1.41</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.12</v>
+        <v>2.56</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.87</v>
+        <v>1.55</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="O6" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="P6" t="n">
-        <v>3.45</v>
+        <v>4.03</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.43</v>
+        <v>2.23</v>
       </c>
       <c r="R6" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U6" t="n">
-        <v>2.33</v>
+        <v>2.28</v>
       </c>
       <c r="V6" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.68</v>
+        <v>1.87</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,80 +1520,80 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.14</v>
+        <v>1.95</v>
       </c>
       <c r="O7" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="P7" t="n">
-        <v>2.89</v>
+        <v>3.44</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.55</v>
+        <v>2.43</v>
       </c>
       <c r="R7" t="n">
-        <v>2.43</v>
+        <v>2.3</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U7" t="n">
-        <v>2.08</v>
+        <v>2.33</v>
       </c>
       <c r="V7" t="n">
-        <v>1.58</v>
+        <v>1.47</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.7</v>
+        <v>3.9</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.48</v>
+        <v>1.64</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.38</v>
+        <v>2.04</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.55</v>
+        <v>1.4</v>
       </c>
       <c r="AE7" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ7" t="n">
         <v>1.21</v>
       </c>
-      <c r="AF7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AK7" t="n">
-        <v>1.55</v>
+        <v>1.68</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.53</v>
+        <v>1.35</v>
       </c>
       <c r="O8" t="n">
-        <v>3.28</v>
+        <v>4.15</v>
       </c>
       <c r="P8" t="n">
-        <v>2.44</v>
+        <v>5.15</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.18</v>
+        <v>1.85</v>
       </c>
       <c r="R8" t="n">
-        <v>2.12</v>
+        <v>2.38</v>
       </c>
       <c r="S8" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="T8" t="n">
-        <v>2.91</v>
+        <v>3.25</v>
       </c>
       <c r="U8" t="n">
-        <v>2.59</v>
+        <v>2.29</v>
       </c>
       <c r="V8" t="n">
-        <v>1.41</v>
+        <v>1.52</v>
       </c>
       <c r="W8" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.92</v>
+        <v>2.35</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.3</v>
+        <v>1.47</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.09</v>
+        <v>1.16</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.63</v>
+        <v>1.77</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.09</v>
+        <v>1.98</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.4</v>
+        <v>2.62</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.4</v>
+        <v>2.35</v>
       </c>
       <c r="O9" t="n">
-        <v>4.4</v>
+        <v>3.27</v>
       </c>
       <c r="P9" t="n">
-        <v>6.32</v>
+        <v>2.25</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.91</v>
+        <v>3.18</v>
       </c>
       <c r="R9" t="n">
-        <v>2.43</v>
+        <v>2.12</v>
       </c>
       <c r="S9" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="T9" t="n">
-        <v>3.25</v>
+        <v>2.91</v>
       </c>
       <c r="U9" t="n">
-        <v>2.29</v>
+        <v>2.71</v>
       </c>
       <c r="V9" t="n">
-        <v>1.52</v>
+        <v>1.41</v>
       </c>
       <c r="W9" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X9" t="n">
         <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.45</v>
+        <v>3.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.35</v>
+        <v>2.92</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.47</v>
+        <v>1.31</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.16</v>
+        <v>1.08</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.78</v>
+        <v>1.63</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.91</v>
+        <v>2.07</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.57</v>
+        <v>1.4</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.66</v>
+        <v>1.52</v>
       </c>
       <c r="O10" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="P10" t="n">
-        <v>4.47</v>
+        <v>4.1</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>

--- a/jogos_2026-06-24.xlsx
+++ b/jogos_2026-06-24.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>15</v>
+        <v>2.3</v>
       </c>
       <c r="O3" t="n">
-        <v>7.6</v>
+        <v>3.46</v>
       </c>
       <c r="P3" t="n">
-        <v>1.11</v>
+        <v>2.57</v>
       </c>
       <c r="Q3" t="n">
-        <v>10</v>
+        <v>2.88</v>
       </c>
       <c r="R3" t="n">
-        <v>3.3</v>
+        <v>2.3</v>
       </c>
       <c r="S3" t="n">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="T3" t="n">
-        <v>4.3</v>
+        <v>3.2</v>
       </c>
       <c r="U3" t="n">
-        <v>1.84</v>
+        <v>2.41</v>
       </c>
       <c r="V3" t="n">
-        <v>1.76</v>
+        <v>1.46</v>
       </c>
       <c r="W3" t="n">
-        <v>1.21</v>
+        <v>1.1</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="Z3" t="n">
-        <v>5.75</v>
+        <v>4.15</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.33</v>
+        <v>1.61</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.88</v>
+        <v>2.08</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.88</v>
+        <v>2.55</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.82</v>
+        <v>1.42</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.33</v>
+        <v>1.15</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.05</v>
+        <v>1.5</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.64</v>
+        <v>2.3</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.06</v>
+        <v>1.39</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.3</v>
+        <v>15</v>
       </c>
       <c r="O4" t="n">
-        <v>3.46</v>
+        <v>7.6</v>
       </c>
       <c r="P4" t="n">
-        <v>2.57</v>
+        <v>1.11</v>
       </c>
       <c r="Q4" t="n">
+        <v>10</v>
+      </c>
+      <c r="R4" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="T4" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AB4" t="n">
         <v>2.88</v>
       </c>
-      <c r="R4" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="S4" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="T4" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U4" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>2.08</v>
-      </c>
       <c r="AC4" t="n">
-        <v>2.55</v>
+        <v>1.88</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.42</v>
+        <v>1.82</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.15</v>
+        <v>1.33</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.5</v>
+        <v>2.05</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.3</v>
+        <v>1.64</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.39</v>
+        <v>1.06</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.53</v>
+        <v>1.01</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,80 +1202,80 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.14</v>
+        <v>1.95</v>
       </c>
       <c r="O5" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="P5" t="n">
-        <v>2.88</v>
+        <v>3.44</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.55</v>
+        <v>2.43</v>
       </c>
       <c r="R5" t="n">
-        <v>2.43</v>
+        <v>2.3</v>
       </c>
       <c r="S5" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="T5" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="U5" t="n">
-        <v>2.08</v>
+        <v>2.33</v>
       </c>
       <c r="V5" t="n">
-        <v>1.58</v>
+        <v>1.47</v>
       </c>
       <c r="W5" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.7</v>
+        <v>3.9</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.48</v>
+        <v>1.64</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.38</v>
+        <v>2.04</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.55</v>
+        <v>1.4</v>
       </c>
       <c r="AE5" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ5" t="n">
         <v>1.21</v>
       </c>
-      <c r="AF5" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AK5" t="n">
-        <v>1.55</v>
+        <v>1.68</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.75</v>
+        <v>2.14</v>
       </c>
       <c r="O6" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="R6" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="T6" t="n">
         <v>3.7</v>
       </c>
-      <c r="P6" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="R6" t="n">
+      <c r="U6" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AB6" t="n">
         <v>2.38</v>
       </c>
-      <c r="S6" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="T6" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U6" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AC6" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.43</v>
+        <v>1.55</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.58</v>
+        <v>1.41</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.12</v>
+        <v>2.56</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.87</v>
+        <v>1.55</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,19 +1520,19 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="O7" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="P7" t="n">
-        <v>3.44</v>
+        <v>4.03</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.43</v>
+        <v>2.23</v>
       </c>
       <c r="R7" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="S7" t="n">
         <v>1.27</v>
@@ -1541,10 +1541,10 @@
         <v>3.2</v>
       </c>
       <c r="U7" t="n">
-        <v>2.33</v>
+        <v>2.28</v>
       </c>
       <c r="V7" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="W7" t="n">
         <v>1.11</v>
@@ -1553,31 +1553,31 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.68</v>
+        <v>1.87</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>

--- a/jogos_2026-06-24.xlsx
+++ b/jogos_2026-06-24.xlsx
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.14</v>
+        <v>1.75</v>
       </c>
       <c r="O6" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P6" t="n">
-        <v>2.88</v>
+        <v>4.03</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.55</v>
+        <v>2.23</v>
       </c>
       <c r="R6" t="n">
-        <v>2.43</v>
+        <v>2.38</v>
       </c>
       <c r="S6" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="T6" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="U6" t="n">
-        <v>2.08</v>
+        <v>2.28</v>
       </c>
       <c r="V6" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AF6" t="n">
         <v>1.58</v>
       </c>
-      <c r="W6" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.41</v>
-      </c>
       <c r="AG6" t="n">
-        <v>2.56</v>
+        <v>2.12</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.55</v>
+        <v>1.87</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.75</v>
+        <v>2.14</v>
       </c>
       <c r="O7" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="R7" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="T7" t="n">
         <v>3.7</v>
       </c>
-      <c r="P7" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="R7" t="n">
+      <c r="U7" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AB7" t="n">
         <v>2.38</v>
       </c>
-      <c r="S7" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="T7" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U7" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AC7" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.43</v>
+        <v>1.55</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.58</v>
+        <v>1.41</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.12</v>
+        <v>2.56</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.87</v>
+        <v>1.55</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.35</v>
+        <v>2.35</v>
       </c>
       <c r="O8" t="n">
-        <v>4.15</v>
+        <v>3.27</v>
       </c>
       <c r="P8" t="n">
-        <v>5.15</v>
+        <v>2.25</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.85</v>
+        <v>3.18</v>
       </c>
       <c r="R8" t="n">
-        <v>2.38</v>
+        <v>2.12</v>
       </c>
       <c r="S8" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="T8" t="n">
-        <v>3.25</v>
+        <v>2.91</v>
       </c>
       <c r="U8" t="n">
-        <v>2.29</v>
+        <v>2.71</v>
       </c>
       <c r="V8" t="n">
-        <v>1.52</v>
+        <v>1.41</v>
       </c>
       <c r="W8" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X8" t="n">
         <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.25</v>
+        <v>1.9</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.35</v>
+        <v>2.92</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.47</v>
+        <v>1.31</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.16</v>
+        <v>1.08</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.77</v>
+        <v>1.63</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.98</v>
+        <v>2.07</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.62</v>
+        <v>1.4</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.35</v>
+        <v>1.35</v>
       </c>
       <c r="O9" t="n">
-        <v>3.27</v>
+        <v>4.15</v>
       </c>
       <c r="P9" t="n">
-        <v>2.25</v>
+        <v>5.15</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.18</v>
+        <v>1.85</v>
       </c>
       <c r="R9" t="n">
-        <v>2.12</v>
+        <v>2.38</v>
       </c>
       <c r="S9" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="T9" t="n">
-        <v>2.91</v>
+        <v>3.25</v>
       </c>
       <c r="U9" t="n">
-        <v>2.71</v>
+        <v>2.29</v>
       </c>
       <c r="V9" t="n">
-        <v>1.41</v>
+        <v>1.52</v>
       </c>
       <c r="W9" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X9" t="n">
         <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.9</v>
+        <v>2.25</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.92</v>
+        <v>2.35</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.31</v>
+        <v>1.47</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.63</v>
+        <v>1.77</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.07</v>
+        <v>1.98</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.4</v>
+        <v>2.62</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>

--- a/jogos_2026-06-24.xlsx
+++ b/jogos_2026-06-24.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,64 +725,64 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -899,7 +899,7 @@
         <v>2.3</v>
       </c>
       <c r="S3" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="T3" t="n">
         <v>3.2</v>
@@ -908,16 +908,16 @@
         <v>2.41</v>
       </c>
       <c r="V3" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="W3" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="Z3" t="n">
         <v>4.15</v>
@@ -926,7 +926,7 @@
         <v>1.61</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AC3" t="n">
         <v>2.55</v>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.39</v>
+        <v>1.25</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>15</v>
+        <v>2.45</v>
       </c>
       <c r="O4" t="n">
-        <v>7.6</v>
+        <v>3.32</v>
       </c>
       <c r="P4" t="n">
-        <v>1.11</v>
+        <v>2.48</v>
       </c>
       <c r="Q4" t="n">
-        <v>10</v>
+        <v>3.04</v>
       </c>
       <c r="R4" t="n">
-        <v>3.3</v>
+        <v>2.11</v>
       </c>
       <c r="S4" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="T4" t="n">
-        <v>4.3</v>
+        <v>2.88</v>
       </c>
       <c r="U4" t="n">
-        <v>1.84</v>
+        <v>2.67</v>
       </c>
       <c r="V4" t="n">
-        <v>1.76</v>
+        <v>1.38</v>
       </c>
       <c r="W4" t="n">
-        <v>1.21</v>
+        <v>1.07</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.08</v>
+        <v>1.24</v>
       </c>
       <c r="Z4" t="n">
-        <v>5.75</v>
+        <v>3.34</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.33</v>
+        <v>1.9</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.88</v>
+        <v>1.9</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.88</v>
+        <v>3.05</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.82</v>
+        <v>1.28</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.33</v>
+        <v>1.07</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.05</v>
+        <v>1.65</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.64</v>
+        <v>2.07</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.06</v>
+        <v>1.24</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.95</v>
+        <v>1.72</v>
       </c>
       <c r="O5" t="n">
-        <v>3.45</v>
+        <v>3.72</v>
       </c>
       <c r="P5" t="n">
-        <v>3.44</v>
+        <v>3.97</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.43</v>
+        <v>2.28</v>
       </c>
       <c r="R5" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="S5" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="T5" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="U5" t="n">
-        <v>2.33</v>
+        <v>2.28</v>
       </c>
       <c r="V5" t="n">
         <v>1.47</v>
       </c>
       <c r="W5" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.68</v>
+        <v>1.91</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,80 +1361,80 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.75</v>
+        <v>2.11</v>
       </c>
       <c r="O6" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="R6" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="T6" t="n">
         <v>3.7</v>
       </c>
-      <c r="P6" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="R6" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="S6" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="T6" t="n">
-        <v>3.2</v>
-      </c>
       <c r="U6" t="n">
-        <v>2.28</v>
+        <v>2.15</v>
       </c>
       <c r="V6" t="n">
-        <v>1.49</v>
+        <v>1.61</v>
       </c>
       <c r="W6" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="Z6" t="n">
-        <v>4</v>
+        <v>5.1</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.1</v>
+        <v>2.43</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.5</v>
+        <v>2.19</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.43</v>
+        <v>1.59</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="AF6" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AK6" t="n">
         <v>1.58</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>1.87</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,80 +1520,80 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.14</v>
+        <v>1.92</v>
       </c>
       <c r="O7" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="P7" t="n">
-        <v>2.88</v>
+        <v>3.34</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="R7" t="n">
-        <v>2.43</v>
+        <v>2.3</v>
       </c>
       <c r="S7" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="T7" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="U7" t="n">
-        <v>2.08</v>
+        <v>2.41</v>
       </c>
       <c r="V7" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="W7" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.7</v>
+        <v>4.15</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.48</v>
+        <v>1.64</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="AC7" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AG7" t="n">
         <v>2.2</v>
       </c>
-      <c r="AD7" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AE7" t="n">
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ7" t="n">
         <v>1.21</v>
       </c>
-      <c r="AF7" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AK7" t="n">
-        <v>1.55</v>
+        <v>1.71</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1682,61 +1682,61 @@
         <v>2.35</v>
       </c>
       <c r="O8" t="n">
-        <v>3.27</v>
+        <v>3.25</v>
       </c>
       <c r="P8" t="n">
         <v>2.25</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.18</v>
+        <v>3.25</v>
       </c>
       <c r="R8" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="S8" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="T8" t="n">
-        <v>2.91</v>
+        <v>2.7</v>
       </c>
       <c r="U8" t="n">
-        <v>2.71</v>
+        <v>2.55</v>
       </c>
       <c r="V8" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="W8" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="X8" t="n">
         <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.8</v>
+        <v>1.98</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.92</v>
+        <v>3.34</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.63</v>
+        <v>1.74</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.07</v>
+        <v>1.93</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,7 +1749,7 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AK8" t="n">
         <v>1.4</v>
@@ -1844,10 +1844,10 @@
         <v>4.15</v>
       </c>
       <c r="P9" t="n">
-        <v>5.15</v>
+        <v>5.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="R9" t="n">
         <v>2.38</v>
@@ -1859,43 +1859,43 @@
         <v>3.25</v>
       </c>
       <c r="U9" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="V9" t="n">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="W9" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="X9" t="n">
         <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="Z9" t="n">
         <v>4.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AB9" t="n">
         <v>2.25</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="AE9" t="n">
         <v>1.16</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.77</v>
+        <v>1.67</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>

--- a/jogos_2026-06-24.xlsx
+++ b/jogos_2026-06-24.xlsx
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.72</v>
+        <v>2.11</v>
       </c>
       <c r="O5" t="n">
-        <v>3.72</v>
+        <v>3.65</v>
       </c>
       <c r="P5" t="n">
-        <v>3.97</v>
+        <v>2.82</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.28</v>
+        <v>2.59</v>
       </c>
       <c r="R5" t="n">
-        <v>2.26</v>
+        <v>2.4</v>
       </c>
       <c r="S5" t="n">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="T5" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="U5" t="n">
-        <v>2.28</v>
+        <v>2.15</v>
       </c>
       <c r="V5" t="n">
-        <v>1.47</v>
+        <v>1.61</v>
       </c>
       <c r="W5" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.1</v>
+        <v>5.1</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.12</v>
+        <v>2.43</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.5</v>
+        <v>2.19</v>
       </c>
       <c r="AD5" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AF5" t="n">
         <v>1.41</v>
       </c>
-      <c r="AE5" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1.59</v>
-      </c>
       <c r="AG5" t="n">
-        <v>2.12</v>
+        <v>2.56</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.91</v>
+        <v>1.58</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,80 +1361,80 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.11</v>
+        <v>1.92</v>
       </c>
       <c r="O6" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="P6" t="n">
-        <v>2.82</v>
+        <v>3.34</v>
       </c>
       <c r="Q6" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R6" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC6" t="n">
         <v>2.59</v>
       </c>
-      <c r="R6" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="S6" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="T6" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="U6" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2.19</v>
-      </c>
       <c r="AD6" t="n">
-        <v>1.59</v>
+        <v>1.39</v>
       </c>
       <c r="AE6" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ6" t="n">
         <v>1.21</v>
       </c>
-      <c r="AF6" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.19</v>
-      </c>
       <c r="AK6" t="n">
-        <v>1.58</v>
+        <v>1.71</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,31 +1520,31 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.92</v>
+        <v>1.72</v>
       </c>
       <c r="O7" t="n">
-        <v>3.55</v>
+        <v>3.72</v>
       </c>
       <c r="P7" t="n">
-        <v>3.34</v>
+        <v>3.97</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.4</v>
+        <v>2.28</v>
       </c>
       <c r="R7" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="S7" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="T7" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="U7" t="n">
-        <v>2.41</v>
+        <v>2.28</v>
       </c>
       <c r="V7" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W7" t="n">
         <v>1.1</v>
@@ -1556,28 +1556,28 @@
         <v>1.16</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.15</v>
+        <v>4.1</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.59</v>
+        <v>2.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.71</v>
+        <v>1.91</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>

--- a/jogos_2026-06-24.xlsx
+++ b/jogos_2026-06-24.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,64 +725,64 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>11.5</v>
+        <v>2.3</v>
       </c>
       <c r="O2" t="n">
-        <v>6.5</v>
+        <v>3.46</v>
       </c>
       <c r="P2" t="n">
-        <v>1.17</v>
+        <v>2.57</v>
       </c>
       <c r="Q2" t="n">
-        <v>10</v>
+        <v>2.88</v>
       </c>
       <c r="R2" t="n">
-        <v>3.3</v>
+        <v>2.3</v>
       </c>
       <c r="S2" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="T2" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="n">
         <v>1.18</v>
       </c>
-      <c r="T2" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1.07</v>
-      </c>
       <c r="Z2" t="n">
-        <v>7</v>
+        <v>4.15</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.32</v>
+        <v>1.61</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.88</v>
+        <v>2.1</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.88</v>
+        <v>2.55</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.81</v>
+        <v>1.42</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.32</v>
+        <v>1.15</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.05</v>
+        <v>1.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.64</v>
+        <v>2.3</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.05</v>
+        <v>1.25</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.3</v>
+        <v>11.5</v>
       </c>
       <c r="O3" t="n">
-        <v>3.46</v>
+        <v>6.5</v>
       </c>
       <c r="P3" t="n">
-        <v>2.57</v>
+        <v>1.17</v>
       </c>
       <c r="Q3" t="n">
+        <v>10</v>
+      </c>
+      <c r="R3" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="T3" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AB3" t="n">
         <v>2.88</v>
       </c>
-      <c r="R3" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="S3" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="T3" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U3" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AC3" t="n">
-        <v>2.55</v>
+        <v>1.88</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.42</v>
+        <v>1.81</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.15</v>
+        <v>1.32</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.5</v>
+        <v>2.05</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.3</v>
+        <v>1.64</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.25</v>
+        <v>1.05</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.45</v>
+        <v>1.01</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,80 +1202,80 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.11</v>
+        <v>1.92</v>
       </c>
       <c r="O5" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="P5" t="n">
-        <v>2.82</v>
+        <v>3.34</v>
       </c>
       <c r="Q5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R5" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC5" t="n">
         <v>2.59</v>
       </c>
-      <c r="R5" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="S5" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="T5" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="U5" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>2.19</v>
-      </c>
       <c r="AD5" t="n">
-        <v>1.59</v>
+        <v>1.39</v>
       </c>
       <c r="AE5" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ5" t="n">
         <v>1.21</v>
       </c>
-      <c r="AF5" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1.19</v>
-      </c>
       <c r="AK5" t="n">
-        <v>1.58</v>
+        <v>1.71</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.92</v>
+        <v>2.11</v>
       </c>
       <c r="O6" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="P6" t="n">
-        <v>3.34</v>
+        <v>2.82</v>
       </c>
       <c r="Q6" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="R6" t="n">
         <v>2.4</v>
       </c>
-      <c r="R6" t="n">
-        <v>2.3</v>
-      </c>
       <c r="S6" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="T6" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="U6" t="n">
-        <v>2.41</v>
+        <v>2.15</v>
       </c>
       <c r="V6" t="n">
-        <v>1.46</v>
+        <v>1.61</v>
       </c>
       <c r="W6" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.15</v>
+        <v>5.1</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.64</v>
+        <v>1.44</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.1</v>
+        <v>2.43</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.59</v>
+        <v>2.19</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.39</v>
+        <v>1.59</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.11</v>
+        <v>1.21</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.56</v>
+        <v>1.41</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.2</v>
+        <v>2.56</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.71</v>
+        <v>1.58</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>

--- a/jogos_2026-06-24.xlsx
+++ b/jogos_2026-06-24.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,64 +725,64 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.3</v>
+        <v>11.5</v>
       </c>
       <c r="O2" t="n">
-        <v>3.46</v>
+        <v>6.5</v>
       </c>
       <c r="P2" t="n">
-        <v>2.57</v>
+        <v>1.17</v>
       </c>
       <c r="Q2" t="n">
+        <v>10</v>
+      </c>
+      <c r="R2" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="S2" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="T2" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AB2" t="n">
         <v>2.88</v>
       </c>
-      <c r="R2" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="S2" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="T2" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U2" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AC2" t="n">
-        <v>2.55</v>
+        <v>1.88</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.42</v>
+        <v>1.81</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.15</v>
+        <v>1.32</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.5</v>
+        <v>2.05</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.3</v>
+        <v>1.64</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.25</v>
+        <v>1.05</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.45</v>
+        <v>1.01</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>11.5</v>
+        <v>2.45</v>
       </c>
       <c r="O3" t="n">
-        <v>6.5</v>
+        <v>3.32</v>
       </c>
       <c r="P3" t="n">
-        <v>1.17</v>
+        <v>2.48</v>
       </c>
       <c r="Q3" t="n">
-        <v>10</v>
+        <v>3.04</v>
       </c>
       <c r="R3" t="n">
-        <v>3.3</v>
+        <v>2.11</v>
       </c>
       <c r="S3" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="T3" t="n">
-        <v>4.3</v>
+        <v>2.88</v>
       </c>
       <c r="U3" t="n">
-        <v>1.94</v>
+        <v>2.67</v>
       </c>
       <c r="V3" t="n">
-        <v>1.75</v>
+        <v>1.38</v>
       </c>
       <c r="W3" t="n">
-        <v>1.21</v>
+        <v>1.07</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y3" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AE3" t="n">
         <v>1.07</v>
       </c>
-      <c r="Z3" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1.32</v>
-      </c>
       <c r="AF3" t="n">
-        <v>2.05</v>
+        <v>1.65</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.64</v>
+        <v>2.07</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.05</v>
+        <v>1.24</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="O4" t="n">
-        <v>3.32</v>
+        <v>3.46</v>
       </c>
       <c r="P4" t="n">
-        <v>2.48</v>
+        <v>2.57</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.04</v>
+        <v>2.88</v>
       </c>
       <c r="R4" t="n">
-        <v>2.11</v>
+        <v>2.3</v>
       </c>
       <c r="S4" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="T4" t="n">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="U4" t="n">
-        <v>2.67</v>
+        <v>2.41</v>
       </c>
       <c r="V4" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="W4" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.34</v>
+        <v>4.15</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.9</v>
+        <v>1.61</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.05</v>
+        <v>2.55</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.28</v>
+        <v>1.42</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.07</v>
+        <v>2.3</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,31 +1202,31 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.92</v>
+        <v>1.72</v>
       </c>
       <c r="O5" t="n">
-        <v>3.55</v>
+        <v>3.72</v>
       </c>
       <c r="P5" t="n">
-        <v>3.34</v>
+        <v>3.97</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.4</v>
+        <v>2.28</v>
       </c>
       <c r="R5" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="S5" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="T5" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="U5" t="n">
-        <v>2.41</v>
+        <v>2.28</v>
       </c>
       <c r="V5" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W5" t="n">
         <v>1.1</v>
@@ -1238,28 +1238,28 @@
         <v>1.16</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.15</v>
+        <v>4.1</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.59</v>
+        <v>2.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.71</v>
+        <v>1.91</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,31 +1520,31 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.72</v>
+        <v>1.92</v>
       </c>
       <c r="O7" t="n">
-        <v>3.72</v>
+        <v>3.55</v>
       </c>
       <c r="P7" t="n">
-        <v>3.97</v>
+        <v>3.34</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="R7" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="S7" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="T7" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="U7" t="n">
-        <v>2.28</v>
+        <v>2.41</v>
       </c>
       <c r="V7" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="W7" t="n">
         <v>1.1</v>
@@ -1556,28 +1556,28 @@
         <v>1.16</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.1</v>
+        <v>4.15</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.5</v>
+        <v>2.59</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.91</v>
+        <v>1.71</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.35</v>
+        <v>1.35</v>
       </c>
       <c r="O8" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="P8" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="R8" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="T8" t="n">
         <v>3.25</v>
       </c>
-      <c r="P8" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="R8" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="S8" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.7</v>
-      </c>
       <c r="U8" t="n">
-        <v>2.55</v>
+        <v>2.28</v>
       </c>
       <c r="V8" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="W8" t="n">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="X8" t="n">
         <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.4</v>
+        <v>4.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.98</v>
+        <v>1.55</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.34</v>
+        <v>2.4</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.24</v>
+        <v>1.53</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.05</v>
+        <v>1.16</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.27</v>
+        <v>1.14</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.4</v>
+        <v>2.7</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.35</v>
+        <v>2.35</v>
       </c>
       <c r="O9" t="n">
-        <v>4.15</v>
+        <v>3.25</v>
       </c>
       <c r="P9" t="n">
-        <v>5.5</v>
+        <v>2.25</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.92</v>
+        <v>3.25</v>
       </c>
       <c r="R9" t="n">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="S9" t="n">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="T9" t="n">
-        <v>3.25</v>
+        <v>2.7</v>
       </c>
       <c r="U9" t="n">
-        <v>2.28</v>
+        <v>2.55</v>
       </c>
       <c r="V9" t="n">
-        <v>1.56</v>
+        <v>1.38</v>
       </c>
       <c r="W9" t="n">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="X9" t="n">
         <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.55</v>
+        <v>1.98</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.4</v>
+        <v>3.34</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.53</v>
+        <v>1.24</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.16</v>
+        <v>1.05</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="AG9" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.7</v>
+        <v>1.4</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>

--- a/jogos_2026-06-24.xlsx
+++ b/jogos_2026-06-24.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,64 +725,64 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>11.5</v>
+        <v>2.35</v>
       </c>
       <c r="O2" t="n">
-        <v>6.5</v>
+        <v>3.35</v>
       </c>
       <c r="P2" t="n">
-        <v>1.17</v>
+        <v>2.4</v>
       </c>
       <c r="Q2" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="R2" t="n">
-        <v>3.3</v>
+        <v>2.1</v>
       </c>
       <c r="S2" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="T2" t="n">
-        <v>4.3</v>
+        <v>2.88</v>
       </c>
       <c r="U2" t="n">
-        <v>1.94</v>
+        <v>2.67</v>
       </c>
       <c r="V2" t="n">
-        <v>1.75</v>
+        <v>1.38</v>
       </c>
       <c r="W2" t="n">
-        <v>1.21</v>
+        <v>1.07</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.07</v>
+        <v>1.24</v>
       </c>
       <c r="Z2" t="n">
-        <v>7</v>
+        <v>3.34</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.32</v>
+        <v>1.95</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.88</v>
+        <v>1.85</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.88</v>
+        <v>3.25</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.81</v>
+        <v>1.33</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.32</v>
+        <v>1.1</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.05</v>
+        <v>1.67</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.64</v>
+        <v>2</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.05</v>
+        <v>1.3</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,80 +884,80 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.45</v>
+        <v>11.5</v>
       </c>
       <c r="O3" t="n">
-        <v>3.32</v>
+        <v>6.5</v>
       </c>
       <c r="P3" t="n">
-        <v>2.48</v>
+        <v>1.17</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.04</v>
+        <v>10</v>
       </c>
       <c r="R3" t="n">
-        <v>2.11</v>
+        <v>3.3</v>
       </c>
       <c r="S3" t="n">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="T3" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AB3" t="n">
         <v>2.88</v>
       </c>
-      <c r="U3" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X3" t="n">
+      <c r="AC3" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AK3" t="n">
         <v>1.01</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ3" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>1.43</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.72</v>
+        <v>2.11</v>
       </c>
       <c r="O5" t="n">
-        <v>3.72</v>
+        <v>3.65</v>
       </c>
       <c r="P5" t="n">
-        <v>3.97</v>
+        <v>2.82</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.28</v>
+        <v>2.59</v>
       </c>
       <c r="R5" t="n">
-        <v>2.26</v>
+        <v>2.4</v>
       </c>
       <c r="S5" t="n">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="T5" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="U5" t="n">
-        <v>2.28</v>
+        <v>2.15</v>
       </c>
       <c r="V5" t="n">
-        <v>1.47</v>
+        <v>1.61</v>
       </c>
       <c r="W5" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.1</v>
+        <v>5.1</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.12</v>
+        <v>2.43</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.5</v>
+        <v>2.19</v>
       </c>
       <c r="AD5" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AF5" t="n">
         <v>1.41</v>
       </c>
-      <c r="AE5" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1.59</v>
-      </c>
       <c r="AG5" t="n">
-        <v>2.12</v>
+        <v>2.56</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.91</v>
+        <v>1.58</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,80 +1361,80 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.11</v>
+        <v>1.92</v>
       </c>
       <c r="O6" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="P6" t="n">
-        <v>2.82</v>
+        <v>3.34</v>
       </c>
       <c r="Q6" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R6" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC6" t="n">
         <v>2.59</v>
       </c>
-      <c r="R6" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="S6" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="T6" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="U6" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2.19</v>
-      </c>
       <c r="AD6" t="n">
-        <v>1.59</v>
+        <v>1.39</v>
       </c>
       <c r="AE6" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ6" t="n">
         <v>1.21</v>
       </c>
-      <c r="AF6" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.19</v>
-      </c>
       <c r="AK6" t="n">
-        <v>1.58</v>
+        <v>1.71</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,31 +1520,31 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.92</v>
+        <v>1.72</v>
       </c>
       <c r="O7" t="n">
-        <v>3.55</v>
+        <v>3.72</v>
       </c>
       <c r="P7" t="n">
-        <v>3.34</v>
+        <v>3.97</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.4</v>
+        <v>2.28</v>
       </c>
       <c r="R7" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="S7" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="T7" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="U7" t="n">
-        <v>2.41</v>
+        <v>2.28</v>
       </c>
       <c r="V7" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W7" t="n">
         <v>1.1</v>
@@ -1556,28 +1556,28 @@
         <v>1.16</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.15</v>
+        <v>4.1</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.59</v>
+        <v>2.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.71</v>
+        <v>1.91</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.35</v>
+        <v>2.35</v>
       </c>
       <c r="O8" t="n">
-        <v>4.15</v>
+        <v>3.25</v>
       </c>
       <c r="P8" t="n">
-        <v>5.5</v>
+        <v>2.25</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.92</v>
+        <v>3.25</v>
       </c>
       <c r="R8" t="n">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="S8" t="n">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="T8" t="n">
-        <v>3.25</v>
+        <v>2.7</v>
       </c>
       <c r="U8" t="n">
-        <v>2.28</v>
+        <v>2.55</v>
       </c>
       <c r="V8" t="n">
-        <v>1.56</v>
+        <v>1.38</v>
       </c>
       <c r="W8" t="n">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="X8" t="n">
         <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.55</v>
+        <v>1.98</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.4</v>
+        <v>3.34</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.53</v>
+        <v>1.24</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.16</v>
+        <v>1.05</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="AG8" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.7</v>
+        <v>1.4</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.35</v>
+        <v>1.35</v>
       </c>
       <c r="O9" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="P9" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="R9" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="T9" t="n">
         <v>3.25</v>
       </c>
-      <c r="P9" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="R9" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="S9" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2.7</v>
-      </c>
       <c r="U9" t="n">
-        <v>2.55</v>
+        <v>2.28</v>
       </c>
       <c r="V9" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="W9" t="n">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="X9" t="n">
         <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.4</v>
+        <v>4.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.98</v>
+        <v>1.55</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.34</v>
+        <v>2.4</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.24</v>
+        <v>1.53</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.05</v>
+        <v>1.16</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.27</v>
+        <v>1.14</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.4</v>
+        <v>2.7</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>

--- a/jogos_2026-06-24.xlsx
+++ b/jogos_2026-06-24.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,64 +725,64 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.35</v>
+        <v>2.18</v>
       </c>
       <c r="O2" t="n">
-        <v>3.35</v>
+        <v>3.18</v>
       </c>
       <c r="P2" t="n">
-        <v>2.4</v>
+        <v>2.47</v>
       </c>
       <c r="Q2" t="n">
-        <v>3</v>
+        <v>2.81</v>
       </c>
       <c r="R2" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="S2" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="T2" t="n">
-        <v>2.88</v>
+        <v>3.3</v>
       </c>
       <c r="U2" t="n">
-        <v>2.67</v>
+        <v>2.41</v>
       </c>
       <c r="V2" t="n">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="W2" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X2" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.34</v>
+        <v>4.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.95</v>
+        <v>1.64</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="AC2" t="n">
-        <v>3.25</v>
+        <v>2.6</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>11.5</v>
+        <v>2.35</v>
       </c>
       <c r="O3" t="n">
-        <v>6.5</v>
+        <v>3.35</v>
       </c>
       <c r="P3" t="n">
-        <v>1.17</v>
+        <v>2.4</v>
       </c>
       <c r="Q3" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="R3" t="n">
-        <v>3.3</v>
+        <v>2.1</v>
       </c>
       <c r="S3" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="T3" t="n">
-        <v>4.3</v>
+        <v>2.88</v>
       </c>
       <c r="U3" t="n">
-        <v>1.94</v>
+        <v>2.67</v>
       </c>
       <c r="V3" t="n">
-        <v>1.75</v>
+        <v>1.38</v>
       </c>
       <c r="W3" t="n">
-        <v>1.21</v>
+        <v>1.07</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.07</v>
+        <v>1.24</v>
       </c>
       <c r="Z3" t="n">
-        <v>7</v>
+        <v>3.34</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.32</v>
+        <v>1.95</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.88</v>
+        <v>1.85</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.88</v>
+        <v>3.25</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.81</v>
+        <v>1.33</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.32</v>
+        <v>1.1</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.05</v>
+        <v>1.67</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.64</v>
+        <v>2</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.05</v>
+        <v>1.3</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.3</v>
+        <v>12</v>
       </c>
       <c r="O4" t="n">
-        <v>3.46</v>
+        <v>6.75</v>
       </c>
       <c r="P4" t="n">
-        <v>2.57</v>
+        <v>1.13</v>
       </c>
       <c r="Q4" t="n">
+        <v>10</v>
+      </c>
+      <c r="R4" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="T4" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AB4" t="n">
         <v>2.88</v>
       </c>
-      <c r="R4" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="S4" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="T4" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U4" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AC4" t="n">
-        <v>2.55</v>
+        <v>1.88</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.42</v>
+        <v>1.81</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.15</v>
+        <v>1.32</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.5</v>
+        <v>2.05</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.3</v>
+        <v>1.64</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.25</v>
+        <v>1.04</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.45</v>
+        <v>1.01</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,80 +1202,80 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="O5" t="n">
-        <v>3.65</v>
+        <v>3.12</v>
       </c>
       <c r="P5" t="n">
-        <v>2.82</v>
+        <v>3.01</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.59</v>
+        <v>2.4</v>
       </c>
       <c r="R5" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="U5" t="n">
         <v>2.4</v>
       </c>
-      <c r="S5" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="T5" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="U5" t="n">
-        <v>2.15</v>
-      </c>
       <c r="V5" t="n">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="W5" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.1</v>
+        <v>4</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.44</v>
+        <v>1.67</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.43</v>
+        <v>2.06</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.19</v>
+        <v>2.6</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.59</v>
+        <v>1.37</v>
       </c>
       <c r="AE5" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ5" t="n">
         <v>1.21</v>
       </c>
-      <c r="AF5" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1.19</v>
-      </c>
       <c r="AK5" t="n">
-        <v>1.58</v>
+        <v>1.7</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,61 +1361,61 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.92</v>
+        <v>1.75</v>
       </c>
       <c r="O6" t="n">
-        <v>3.55</v>
+        <v>3.17</v>
       </c>
       <c r="P6" t="n">
-        <v>3.34</v>
+        <v>3.37</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="R6" t="n">
         <v>2.3</v>
       </c>
       <c r="S6" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="T6" t="n">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="U6" t="n">
-        <v>2.41</v>
+        <v>2.28</v>
       </c>
       <c r="V6" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="W6" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y6" t="n">
         <v>1.16</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.15</v>
+        <v>4.1</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AB6" t="n">
         <v>2.1</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="AG6" t="n">
         <v>2.2</v>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.71</v>
+        <v>1.87</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.72</v>
+        <v>2.11</v>
       </c>
       <c r="O7" t="n">
-        <v>3.72</v>
+        <v>3.6</v>
       </c>
       <c r="P7" t="n">
-        <v>3.97</v>
+        <v>2.49</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.28</v>
+        <v>2.57</v>
       </c>
       <c r="R7" t="n">
-        <v>2.26</v>
+        <v>2.4</v>
       </c>
       <c r="S7" t="n">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="T7" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="U7" t="n">
-        <v>2.28</v>
+        <v>2.15</v>
       </c>
       <c r="V7" t="n">
-        <v>1.47</v>
+        <v>1.61</v>
       </c>
       <c r="W7" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.1</v>
+        <v>5.5</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.12</v>
+        <v>2.43</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.41</v>
+        <v>1.59</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.59</v>
+        <v>1.4</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.12</v>
+        <v>2.75</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.91</v>
+        <v>1.58</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.35</v>
+        <v>1.36</v>
       </c>
       <c r="O8" t="n">
-        <v>3.25</v>
+        <v>4.7</v>
       </c>
       <c r="P8" t="n">
-        <v>2.25</v>
+        <v>5.6</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.25</v>
+        <v>1.85</v>
       </c>
       <c r="R8" t="n">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="S8" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="T8" t="n">
-        <v>2.7</v>
+        <v>3.28</v>
       </c>
       <c r="U8" t="n">
-        <v>2.55</v>
+        <v>2.23</v>
       </c>
       <c r="V8" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="W8" t="n">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="X8" t="n">
         <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.4</v>
+        <v>4.65</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.98</v>
+        <v>1.57</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.95</v>
+        <v>2.27</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.34</v>
+        <v>2.28</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.24</v>
+        <v>1.54</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.05</v>
+        <v>1.18</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.27</v>
+        <v>1.12</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.4</v>
+        <v>2.64</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.35</v>
+        <v>2.26</v>
       </c>
       <c r="O9" t="n">
-        <v>4.15</v>
+        <v>3.22</v>
       </c>
       <c r="P9" t="n">
-        <v>5.5</v>
+        <v>2.87</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.92</v>
+        <v>2.98</v>
       </c>
       <c r="R9" t="n">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="S9" t="n">
-        <v>1.27</v>
+        <v>1.37</v>
       </c>
       <c r="T9" t="n">
-        <v>3.25</v>
+        <v>2.98</v>
       </c>
       <c r="U9" t="n">
-        <v>2.28</v>
+        <v>2.88</v>
       </c>
       <c r="V9" t="n">
-        <v>1.56</v>
+        <v>1.39</v>
       </c>
       <c r="W9" t="n">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="X9" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.55</v>
+        <v>1.87</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.25</v>
+        <v>1.85</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.53</v>
+        <v>1.26</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.16</v>
+        <v>1.06</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.67</v>
+        <v>1.81</v>
       </c>
       <c r="AG9" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.14</v>
+        <v>1.26</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.7</v>
+        <v>1.51</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -2006,55 +2006,55 @@
         <v>4.1</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>

--- a/jogos_2026-06-24.xlsx
+++ b/jogos_2026-06-24.xlsx
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.9</v>
+        <v>2.11</v>
       </c>
       <c r="O5" t="n">
-        <v>3.12</v>
+        <v>3.6</v>
       </c>
       <c r="P5" t="n">
-        <v>3.01</v>
+        <v>2.49</v>
       </c>
       <c r="Q5" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="R5" t="n">
         <v>2.4</v>
       </c>
-      <c r="R5" t="n">
-        <v>2.3</v>
-      </c>
       <c r="S5" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="T5" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="U5" t="n">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="V5" t="n">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="W5" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="X5" t="n">
         <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="Z5" t="n">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.67</v>
+        <v>1.44</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.06</v>
+        <v>2.43</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.37</v>
+        <v>1.59</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.7</v>
+        <v>1.58</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="O6" t="n">
-        <v>3.17</v>
+        <v>3.12</v>
       </c>
       <c r="P6" t="n">
-        <v>3.37</v>
+        <v>3.01</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="R6" t="n">
         <v>2.3</v>
       </c>
       <c r="S6" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="T6" t="n">
-        <v>3.14</v>
+        <v>3.6</v>
       </c>
       <c r="U6" t="n">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="V6" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W6" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X6" t="n">
         <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="AC6" t="n">
         <v>2.6</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.87</v>
+        <v>1.7</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,65 +1520,65 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.11</v>
+        <v>1.75</v>
       </c>
       <c r="O7" t="n">
-        <v>3.6</v>
+        <v>3.17</v>
       </c>
       <c r="P7" t="n">
-        <v>2.49</v>
+        <v>3.37</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.57</v>
+        <v>2.25</v>
       </c>
       <c r="R7" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="S7" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="T7" t="n">
-        <v>3.7</v>
+        <v>3.14</v>
       </c>
       <c r="U7" t="n">
-        <v>2.15</v>
+        <v>2.28</v>
       </c>
       <c r="V7" t="n">
-        <v>1.61</v>
+        <v>1.49</v>
       </c>
       <c r="W7" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="X7" t="n">
         <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.5</v>
+        <v>4.1</v>
       </c>
       <c r="AA7" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AD7" t="n">
         <v>1.44</v>
       </c>
-      <c r="AB7" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AC7" t="n">
+      <c r="AE7" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AG7" t="n">
         <v>2.2</v>
       </c>
-      <c r="AD7" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>2.75</v>
-      </c>
       <c r="AH7" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.58</v>
+        <v>1.87</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>

--- a/jogos_2026-06-24.xlsx
+++ b/jogos_2026-06-24.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,65 +725,65 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.18</v>
+        <v>12</v>
       </c>
       <c r="O2" t="n">
-        <v>3.18</v>
+        <v>6.75</v>
       </c>
       <c r="P2" t="n">
-        <v>2.47</v>
+        <v>1.13</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.81</v>
+        <v>10</v>
       </c>
       <c r="R2" t="n">
-        <v>2.2</v>
+        <v>3.3</v>
       </c>
       <c r="S2" t="n">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="T2" t="n">
-        <v>3.3</v>
+        <v>4.3</v>
       </c>
       <c r="U2" t="n">
-        <v>2.41</v>
+        <v>1.91</v>
       </c>
       <c r="V2" t="n">
-        <v>1.46</v>
+        <v>1.8</v>
       </c>
       <c r="W2" t="n">
-        <v>1.1</v>
+        <v>1.21</v>
       </c>
       <c r="X2" t="n">
         <v>1.01</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.17</v>
+        <v>1.07</v>
       </c>
       <c r="Z2" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="AA2" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AG2" t="n">
         <v>1.64</v>
       </c>
-      <c r="AB2" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>2.3</v>
-      </c>
       <c r="AH2" t="inlineStr">
         <is>
           <t>[]</t>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.44</v>
+        <v>1.04</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.52</v>
+        <v>1.01</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>12</v>
+        <v>2.18</v>
       </c>
       <c r="O4" t="n">
-        <v>6.75</v>
+        <v>3.18</v>
       </c>
       <c r="P4" t="n">
-        <v>1.13</v>
+        <v>2.47</v>
       </c>
       <c r="Q4" t="n">
-        <v>10</v>
+        <v>2.81</v>
       </c>
       <c r="R4" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="T4" t="n">
         <v>3.3</v>
       </c>
-      <c r="S4" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="T4" t="n">
-        <v>4.3</v>
-      </c>
       <c r="U4" t="n">
-        <v>1.91</v>
+        <v>2.41</v>
       </c>
       <c r="V4" t="n">
-        <v>1.8</v>
+        <v>1.46</v>
       </c>
       <c r="W4" t="n">
-        <v>1.21</v>
+        <v>1.1</v>
       </c>
       <c r="X4" t="n">
         <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.07</v>
+        <v>1.17</v>
       </c>
       <c r="Z4" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.32</v>
+        <v>1.64</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.88</v>
+        <v>2.2</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.88</v>
+        <v>2.6</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.81</v>
+        <v>1.44</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.32</v>
+        <v>1.13</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.05</v>
+        <v>1.5</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.64</v>
+        <v>2.3</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.04</v>
+        <v>1.44</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,65 +1202,65 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.11</v>
+        <v>1.75</v>
       </c>
       <c r="O5" t="n">
-        <v>3.6</v>
+        <v>3.17</v>
       </c>
       <c r="P5" t="n">
-        <v>2.49</v>
+        <v>3.37</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.57</v>
+        <v>2.25</v>
       </c>
       <c r="R5" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="S5" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="T5" t="n">
-        <v>3.7</v>
+        <v>3.14</v>
       </c>
       <c r="U5" t="n">
-        <v>2.15</v>
+        <v>2.28</v>
       </c>
       <c r="V5" t="n">
-        <v>1.61</v>
+        <v>1.49</v>
       </c>
       <c r="W5" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="X5" t="n">
         <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.5</v>
+        <v>4.1</v>
       </c>
       <c r="AA5" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AD5" t="n">
         <v>1.44</v>
       </c>
-      <c r="AB5" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AC5" t="n">
+      <c r="AE5" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AG5" t="n">
         <v>2.2</v>
       </c>
-      <c r="AD5" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>2.75</v>
-      </c>
       <c r="AH5" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.58</v>
+        <v>1.87</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.9</v>
+        <v>2.11</v>
       </c>
       <c r="O6" t="n">
-        <v>3.12</v>
+        <v>3.6</v>
       </c>
       <c r="P6" t="n">
-        <v>3.01</v>
+        <v>2.49</v>
       </c>
       <c r="Q6" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="R6" t="n">
         <v>2.4</v>
       </c>
-      <c r="R6" t="n">
-        <v>2.3</v>
-      </c>
       <c r="S6" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="T6" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="U6" t="n">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="V6" t="n">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="W6" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="X6" t="n">
         <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="Z6" t="n">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.67</v>
+        <v>1.44</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.06</v>
+        <v>2.43</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.37</v>
+        <v>1.59</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.7</v>
+        <v>1.58</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="O7" t="n">
-        <v>3.17</v>
+        <v>3.12</v>
       </c>
       <c r="P7" t="n">
-        <v>3.37</v>
+        <v>3.01</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="R7" t="n">
         <v>2.3</v>
       </c>
       <c r="S7" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="T7" t="n">
-        <v>3.14</v>
+        <v>3.6</v>
       </c>
       <c r="U7" t="n">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="V7" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W7" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X7" t="n">
         <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="AC7" t="n">
         <v>2.6</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.87</v>
+        <v>1.7</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>

--- a/jogos_2026-06-24.xlsx
+++ b/jogos_2026-06-24.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,64 +725,64 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>12</v>
+        <v>2.18</v>
       </c>
       <c r="O2" t="n">
-        <v>6.75</v>
+        <v>3.18</v>
       </c>
       <c r="P2" t="n">
-        <v>1.13</v>
+        <v>2.47</v>
       </c>
       <c r="Q2" t="n">
-        <v>10</v>
+        <v>2.81</v>
       </c>
       <c r="R2" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S2" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="T2" t="n">
         <v>3.3</v>
       </c>
-      <c r="S2" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="T2" t="n">
-        <v>4.3</v>
-      </c>
       <c r="U2" t="n">
-        <v>1.91</v>
+        <v>2.41</v>
       </c>
       <c r="V2" t="n">
-        <v>1.8</v>
+        <v>1.46</v>
       </c>
       <c r="W2" t="n">
-        <v>1.21</v>
+        <v>1.1</v>
       </c>
       <c r="X2" t="n">
         <v>1.01</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.07</v>
+        <v>1.17</v>
       </c>
       <c r="Z2" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.32</v>
+        <v>1.64</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.88</v>
+        <v>2.2</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.88</v>
+        <v>2.6</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.81</v>
+        <v>1.44</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.32</v>
+        <v>1.13</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.05</v>
+        <v>1.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.64</v>
+        <v>2.3</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.04</v>
+        <v>1.44</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,65 +1043,65 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.18</v>
+        <v>12</v>
       </c>
       <c r="O4" t="n">
-        <v>3.18</v>
+        <v>6.75</v>
       </c>
       <c r="P4" t="n">
-        <v>2.47</v>
+        <v>1.13</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.81</v>
+        <v>10</v>
       </c>
       <c r="R4" t="n">
-        <v>2.2</v>
+        <v>3.3</v>
       </c>
       <c r="S4" t="n">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="T4" t="n">
-        <v>3.3</v>
+        <v>4.3</v>
       </c>
       <c r="U4" t="n">
-        <v>2.41</v>
+        <v>1.91</v>
       </c>
       <c r="V4" t="n">
-        <v>1.46</v>
+        <v>1.8</v>
       </c>
       <c r="W4" t="n">
-        <v>1.1</v>
+        <v>1.21</v>
       </c>
       <c r="X4" t="n">
         <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.17</v>
+        <v>1.07</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="AA4" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AG4" t="n">
         <v>1.64</v>
       </c>
-      <c r="AB4" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>2.3</v>
-      </c>
       <c r="AH4" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.44</v>
+        <v>1.04</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.52</v>
+        <v>1.01</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="O5" t="n">
-        <v>3.17</v>
+        <v>3.12</v>
       </c>
       <c r="P5" t="n">
-        <v>3.37</v>
+        <v>3.01</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="R5" t="n">
         <v>2.3</v>
       </c>
       <c r="S5" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="T5" t="n">
-        <v>3.14</v>
+        <v>3.6</v>
       </c>
       <c r="U5" t="n">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="V5" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W5" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X5" t="n">
         <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="AC5" t="n">
         <v>2.6</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.87</v>
+        <v>1.7</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="O7" t="n">
-        <v>3.12</v>
+        <v>3.17</v>
       </c>
       <c r="P7" t="n">
-        <v>3.01</v>
+        <v>3.37</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="R7" t="n">
         <v>2.3</v>
       </c>
       <c r="S7" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="T7" t="n">
-        <v>3.6</v>
+        <v>3.14</v>
       </c>
       <c r="U7" t="n">
-        <v>2.4</v>
+        <v>2.28</v>
       </c>
       <c r="V7" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="W7" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X7" t="n">
         <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="Z7" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="AC7" t="n">
         <v>2.6</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.7</v>
+        <v>1.87</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.36</v>
+        <v>2.26</v>
       </c>
       <c r="O8" t="n">
-        <v>4.7</v>
+        <v>3.22</v>
       </c>
       <c r="P8" t="n">
-        <v>5.6</v>
+        <v>2.87</v>
       </c>
       <c r="Q8" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="R8" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AB8" t="n">
         <v>1.85</v>
       </c>
-      <c r="R8" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="S8" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="T8" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="U8" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>2.27</v>
-      </c>
       <c r="AC8" t="n">
-        <v>2.28</v>
+        <v>3.2</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.54</v>
+        <v>1.26</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.18</v>
+        <v>1.06</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.94</v>
+        <v>1.87</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.12</v>
+        <v>1.26</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.64</v>
+        <v>1.51</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.26</v>
+        <v>1.36</v>
       </c>
       <c r="O9" t="n">
-        <v>3.22</v>
+        <v>4.7</v>
       </c>
       <c r="P9" t="n">
-        <v>2.87</v>
+        <v>5.6</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.98</v>
+        <v>1.85</v>
       </c>
       <c r="R9" t="n">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="S9" t="n">
-        <v>1.37</v>
+        <v>1.25</v>
       </c>
       <c r="T9" t="n">
-        <v>2.98</v>
+        <v>3.28</v>
       </c>
       <c r="U9" t="n">
-        <v>2.88</v>
+        <v>2.23</v>
       </c>
       <c r="V9" t="n">
-        <v>1.39</v>
+        <v>1.56</v>
       </c>
       <c r="W9" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.29</v>
+        <v>1.14</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.4</v>
+        <v>4.65</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.87</v>
+        <v>1.57</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.85</v>
+        <v>2.27</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.2</v>
+        <v>2.28</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.26</v>
+        <v>1.54</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.81</v>
+        <v>1.73</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.26</v>
+        <v>1.12</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.51</v>
+        <v>2.64</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>

--- a/jogos_2026-06-24.xlsx
+++ b/jogos_2026-06-24.xlsx
@@ -725,58 +725,58 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.18</v>
+        <v>1.98</v>
       </c>
       <c r="O2" t="n">
         <v>3.18</v>
       </c>
       <c r="P2" t="n">
-        <v>2.47</v>
+        <v>2.8</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.81</v>
+        <v>2.65</v>
       </c>
       <c r="R2" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="S2" t="n">
         <v>1.29</v>
       </c>
       <c r="T2" t="n">
-        <v>3.3</v>
+        <v>3.08</v>
       </c>
       <c r="U2" t="n">
-        <v>2.41</v>
+        <v>2.25</v>
       </c>
       <c r="V2" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="W2" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="Z2" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.2</v>
+        <v>2.01</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.6</v>
+        <v>2.74</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AF2" t="n">
         <v>1.5</v>
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.44</v>
+        <v>1.22</v>
       </c>
       <c r="AK2" t="n">
         <v>1.52</v>
@@ -884,16 +884,16 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.35</v>
+        <v>2.75</v>
       </c>
       <c r="O3" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="P3" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="Q3" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="R3" t="n">
         <v>2.1</v>
@@ -905,59 +905,59 @@
         <v>2.88</v>
       </c>
       <c r="U3" t="n">
-        <v>2.67</v>
+        <v>2.6</v>
       </c>
       <c r="V3" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W3" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X3" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y3" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ3" t="n">
         <v>1.24</v>
       </c>
-      <c r="Z3" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AD3" t="n">
+      <c r="AK3" t="n">
         <v>1.33</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>1.44</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1043,10 +1043,10 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O4" t="n">
-        <v>6.75</v>
+        <v>7</v>
       </c>
       <c r="P4" t="n">
         <v>1.13</v>
@@ -1058,43 +1058,43 @@
         <v>3.3</v>
       </c>
       <c r="S4" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="T4" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="U4" t="n">
-        <v>1.91</v>
+        <v>2.06</v>
       </c>
       <c r="V4" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="W4" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="X4" t="n">
         <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Z4" t="n">
-        <v>7</v>
+        <v>5.75</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.88</v>
+        <v>2.59</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.88</v>
+        <v>2.04</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.81</v>
+        <v>1.68</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AF4" t="n">
         <v>2.05</v>
@@ -1113,7 +1113,7 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AK4" t="n">
         <v>1.01</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,19 +1202,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.9</v>
+        <v>1.55</v>
       </c>
       <c r="O5" t="n">
-        <v>3.12</v>
+        <v>3.4</v>
       </c>
       <c r="P5" t="n">
-        <v>3.01</v>
+        <v>5.22</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.4</v>
+        <v>2.23</v>
       </c>
       <c r="R5" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="S5" t="n">
         <v>1.25</v>
@@ -1223,43 +1223,43 @@
         <v>3.6</v>
       </c>
       <c r="U5" t="n">
-        <v>2.4</v>
+        <v>2.28</v>
       </c>
       <c r="V5" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="W5" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z5" t="n">
         <v>4</v>
       </c>
       <c r="AA5" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AF5" t="n">
         <v>1.67</v>
       </c>
-      <c r="AB5" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AG5" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.7</v>
+        <v>1.87</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.11</v>
+        <v>2.14</v>
       </c>
       <c r="O6" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="R6" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T6" t="n">
         <v>3.6</v>
       </c>
-      <c r="P6" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="R6" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="S6" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="T6" t="n">
-        <v>3.7</v>
-      </c>
       <c r="U6" t="n">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="V6" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="W6" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="X6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="Z6" t="n">
-        <v>5.5</v>
+        <v>4.7</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.43</v>
+        <v>2.38</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.59</v>
+        <v>1.48</v>
       </c>
       <c r="AE6" t="n">
         <v>1.21</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.75</v>
+        <v>2.36</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.75</v>
+        <v>1.96</v>
       </c>
       <c r="O7" t="n">
-        <v>3.17</v>
+        <v>3.5</v>
       </c>
       <c r="P7" t="n">
-        <v>3.37</v>
+        <v>3.41</v>
       </c>
       <c r="Q7" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="R7" t="n">
         <v>2.25</v>
       </c>
-      <c r="R7" t="n">
-        <v>2.3</v>
-      </c>
       <c r="S7" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="T7" t="n">
-        <v>3.14</v>
+        <v>3</v>
       </c>
       <c r="U7" t="n">
-        <v>2.28</v>
+        <v>2.71</v>
       </c>
       <c r="V7" t="n">
-        <v>1.49</v>
+        <v>1.43</v>
       </c>
       <c r="W7" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X7" t="n">
         <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.1</v>
+        <v>3.65</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.1</v>
+        <v>1.94</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF7" t="n">
         <v>1.6</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.87</v>
+        <v>1.64</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="O8" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="P8" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="R8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="U8" t="n">
         <v>2.26</v>
       </c>
-      <c r="O8" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="P8" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="R8" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="S8" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="U8" t="n">
-        <v>2.88</v>
-      </c>
       <c r="V8" t="n">
-        <v>1.39</v>
+        <v>1.56</v>
       </c>
       <c r="W8" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.29</v>
+        <v>1.17</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.4</v>
+        <v>5</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.87</v>
+        <v>1.57</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.85</v>
+        <v>2.35</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.2</v>
+        <v>2.29</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.26</v>
+        <v>1.53</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.06</v>
+        <v>1.17</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.81</v>
+        <v>1.73</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.26</v>
+        <v>1.13</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.51</v>
+        <v>2.6</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,80 +1838,80 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.36</v>
+        <v>2.1</v>
       </c>
       <c r="O9" t="n">
-        <v>4.7</v>
+        <v>3.2</v>
       </c>
       <c r="P9" t="n">
-        <v>5.6</v>
+        <v>2.6</v>
       </c>
       <c r="Q9" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R9" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AA9" t="n">
         <v>1.85</v>
       </c>
-      <c r="R9" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="S9" t="n">
+      <c r="AB9" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ9" t="n">
         <v>1.25</v>
       </c>
-      <c r="T9" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="U9" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1.12</v>
-      </c>
       <c r="AK9" t="n">
-        <v>2.64</v>
+        <v>1.51</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -2009,37 +2009,37 @@
         <v>2.21</v>
       </c>
       <c r="R10" t="n">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="S10" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T10" t="n">
-        <v>3.1</v>
+        <v>2.81</v>
       </c>
       <c r="U10" t="n">
-        <v>2.62</v>
+        <v>2.51</v>
       </c>
       <c r="V10" t="n">
         <v>1.4</v>
       </c>
       <c r="W10" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X10" t="n">
         <v>1.04</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AC10" t="n">
         <v>3.04</v>
@@ -2051,7 +2051,7 @@
         <v>1.07</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="AG10" t="n">
         <v>1.92</v>

--- a/jogos_2026-06-24.xlsx
+++ b/jogos_2026-06-24.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,64 +725,64 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>1.98</v>
+        <v>2.75</v>
       </c>
       <c r="O2" t="n">
-        <v>3.18</v>
+        <v>3.25</v>
       </c>
       <c r="P2" t="n">
-        <v>2.8</v>
+        <v>2.25</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.65</v>
+        <v>3.2</v>
       </c>
       <c r="R2" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="S2" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="T2" t="n">
-        <v>3.08</v>
+        <v>2.88</v>
       </c>
       <c r="U2" t="n">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="V2" t="n">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="W2" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X2" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y2" t="n">
         <v>1.22</v>
       </c>
       <c r="Z2" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.74</v>
+        <v>2.9</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.3</v>
+        <v>2.08</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.52</v>
+        <v>1.33</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.75</v>
+        <v>13</v>
       </c>
       <c r="O3" t="n">
-        <v>3.25</v>
+        <v>7</v>
       </c>
       <c r="P3" t="n">
-        <v>2.25</v>
+        <v>1.13</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.2</v>
+        <v>10</v>
       </c>
       <c r="R3" t="n">
-        <v>2.1</v>
+        <v>3.3</v>
       </c>
       <c r="S3" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="T3" t="n">
-        <v>2.88</v>
+        <v>4</v>
       </c>
       <c r="U3" t="n">
-        <v>2.6</v>
+        <v>2.06</v>
       </c>
       <c r="V3" t="n">
-        <v>1.4</v>
+        <v>1.76</v>
       </c>
       <c r="W3" t="n">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="X3" t="n">
         <v>1.01</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.22</v>
+        <v>1.08</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.8</v>
+        <v>5.75</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.85</v>
+        <v>1.39</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.95</v>
+        <v>2.59</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.9</v>
+        <v>2.04</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.32</v>
+        <v>1.68</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.08</v>
+        <v>1.33</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.62</v>
+        <v>2.05</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.08</v>
+        <v>1.64</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.24</v>
+        <v>1.05</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>13</v>
+        <v>1.98</v>
       </c>
       <c r="O4" t="n">
-        <v>7</v>
+        <v>3.18</v>
       </c>
       <c r="P4" t="n">
-        <v>1.13</v>
+        <v>2.8</v>
       </c>
       <c r="Q4" t="n">
-        <v>10</v>
+        <v>2.65</v>
       </c>
       <c r="R4" t="n">
-        <v>3.3</v>
+        <v>2.3</v>
       </c>
       <c r="S4" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="T4" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z4" t="n">
         <v>4</v>
       </c>
-      <c r="U4" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>5.75</v>
-      </c>
       <c r="AA4" t="n">
-        <v>1.39</v>
+        <v>1.7</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.59</v>
+        <v>2.01</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.04</v>
+        <v>2.74</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.68</v>
+        <v>1.38</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.33</v>
+        <v>1.15</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.05</v>
+        <v>1.5</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.64</v>
+        <v>2.3</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.05</v>
+        <v>1.22</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,61 +1202,61 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.55</v>
+        <v>1.96</v>
       </c>
       <c r="O5" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P5" t="n">
-        <v>5.22</v>
+        <v>3.41</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.23</v>
+        <v>2.32</v>
       </c>
       <c r="R5" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="S5" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="T5" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="U5" t="n">
-        <v>2.28</v>
+        <v>2.71</v>
       </c>
       <c r="V5" t="n">
-        <v>1.49</v>
+        <v>1.43</v>
       </c>
       <c r="W5" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="Z5" t="n">
-        <v>4</v>
+        <v>3.65</v>
       </c>
       <c r="AA5" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AF5" t="n">
         <v>1.6</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1.67</v>
       </c>
       <c r="AG5" t="n">
         <v>2.1</v>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.87</v>
+        <v>1.64</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,19 +1361,19 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.14</v>
+        <v>1.55</v>
       </c>
       <c r="O6" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="P6" t="n">
-        <v>2.5</v>
+        <v>5.22</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.63</v>
+        <v>2.23</v>
       </c>
       <c r="R6" t="n">
-        <v>2.43</v>
+        <v>2.38</v>
       </c>
       <c r="S6" t="n">
         <v>1.25</v>
@@ -1382,10 +1382,10 @@
         <v>3.6</v>
       </c>
       <c r="U6" t="n">
-        <v>2.08</v>
+        <v>2.28</v>
       </c>
       <c r="V6" t="n">
-        <v>1.58</v>
+        <v>1.49</v>
       </c>
       <c r="W6" t="n">
         <v>1.11</v>
@@ -1394,31 +1394,31 @@
         <v>1.03</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.7</v>
+        <v>4</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.48</v>
+        <v>1.6</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.38</v>
+        <v>2.15</v>
       </c>
       <c r="AC6" t="n">
         <v>2.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.48</v>
+        <v>1.67</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.36</v>
+        <v>2.1</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.55</v>
+        <v>1.87</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.96</v>
+        <v>2.14</v>
       </c>
       <c r="O7" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="P7" t="n">
-        <v>3.41</v>
+        <v>2.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.32</v>
+        <v>2.63</v>
       </c>
       <c r="R7" t="n">
-        <v>2.25</v>
+        <v>2.43</v>
       </c>
       <c r="S7" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="T7" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="U7" t="n">
-        <v>2.71</v>
+        <v>2.08</v>
       </c>
       <c r="V7" t="n">
-        <v>1.43</v>
+        <v>1.58</v>
       </c>
       <c r="W7" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y7" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AE7" t="n">
         <v>1.21</v>
       </c>
-      <c r="Z7" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.12</v>
-      </c>
       <c r="AF7" t="n">
-        <v>1.6</v>
+        <v>1.48</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.1</v>
+        <v>2.36</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.64</v>
+        <v>1.55</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,80 +1679,80 @@
         </is>
       </c>
       <c r="N8" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="O8" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R8" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="S8" t="n">
         <v>1.35</v>
       </c>
-      <c r="O8" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="P8" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="R8" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="S8" t="n">
+      <c r="T8" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ8" t="n">
         <v>1.25</v>
       </c>
-      <c r="T8" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="U8" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1.13</v>
-      </c>
       <c r="AK8" t="n">
-        <v>2.6</v>
+        <v>1.51</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,80 +1838,80 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.1</v>
+        <v>1.35</v>
       </c>
       <c r="O9" t="n">
-        <v>3.2</v>
+        <v>4.15</v>
       </c>
       <c r="P9" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="R9" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AK9" t="n">
         <v>2.6</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R9" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="S9" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="U9" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>3.19</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>1.51</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>

--- a/jogos_2026-06-24.xlsx
+++ b/jogos_2026-06-24.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>13</v>
+        <v>1.98</v>
       </c>
       <c r="O3" t="n">
-        <v>7</v>
+        <v>3.18</v>
       </c>
       <c r="P3" t="n">
-        <v>1.13</v>
+        <v>2.8</v>
       </c>
       <c r="Q3" t="n">
-        <v>10</v>
+        <v>2.65</v>
       </c>
       <c r="R3" t="n">
-        <v>3.3</v>
+        <v>2.3</v>
       </c>
       <c r="S3" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="T3" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z3" t="n">
         <v>4</v>
       </c>
-      <c r="U3" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>5.75</v>
-      </c>
       <c r="AA3" t="n">
-        <v>1.39</v>
+        <v>1.7</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.59</v>
+        <v>2.01</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.04</v>
+        <v>2.74</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.68</v>
+        <v>1.38</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.33</v>
+        <v>1.15</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.05</v>
+        <v>1.5</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.64</v>
+        <v>2.3</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.05</v>
+        <v>1.22</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.98</v>
+        <v>13</v>
       </c>
       <c r="O4" t="n">
-        <v>3.18</v>
+        <v>7</v>
       </c>
       <c r="P4" t="n">
-        <v>2.8</v>
+        <v>1.13</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.65</v>
+        <v>10</v>
       </c>
       <c r="R4" t="n">
-        <v>2.3</v>
+        <v>3.3</v>
       </c>
       <c r="S4" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="T4" t="n">
-        <v>3.08</v>
+        <v>4</v>
       </c>
       <c r="U4" t="n">
-        <v>2.25</v>
+        <v>2.06</v>
       </c>
       <c r="V4" t="n">
-        <v>1.49</v>
+        <v>1.76</v>
       </c>
       <c r="W4" t="n">
-        <v>1.09</v>
+        <v>1.2</v>
       </c>
       <c r="X4" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.22</v>
+        <v>1.08</v>
       </c>
       <c r="Z4" t="n">
-        <v>4</v>
+        <v>5.75</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.7</v>
+        <v>1.39</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.01</v>
+        <v>2.59</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.74</v>
+        <v>2.04</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.38</v>
+        <v>1.68</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.15</v>
+        <v>1.33</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.5</v>
+        <v>2.05</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.3</v>
+        <v>1.64</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.22</v>
+        <v>1.05</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.52</v>
+        <v>1.01</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,61 +1202,61 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.96</v>
+        <v>1.55</v>
       </c>
       <c r="O5" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P5" t="n">
-        <v>3.41</v>
+        <v>5.22</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.32</v>
+        <v>2.23</v>
       </c>
       <c r="R5" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="S5" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="T5" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="U5" t="n">
-        <v>2.71</v>
+        <v>2.28</v>
       </c>
       <c r="V5" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AD5" t="n">
         <v>1.43</v>
       </c>
-      <c r="W5" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AE5" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AG5" t="n">
         <v>2.1</v>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.64</v>
+        <v>1.87</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,19 +1361,19 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.55</v>
+        <v>2.14</v>
       </c>
       <c r="O6" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="P6" t="n">
-        <v>5.22</v>
+        <v>2.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.23</v>
+        <v>2.63</v>
       </c>
       <c r="R6" t="n">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="S6" t="n">
         <v>1.25</v>
@@ -1382,10 +1382,10 @@
         <v>3.6</v>
       </c>
       <c r="U6" t="n">
-        <v>2.28</v>
+        <v>2.08</v>
       </c>
       <c r="V6" t="n">
-        <v>1.49</v>
+        <v>1.58</v>
       </c>
       <c r="W6" t="n">
         <v>1.11</v>
@@ -1394,31 +1394,31 @@
         <v>1.03</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="Z6" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.6</v>
+        <v>1.48</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.15</v>
+        <v>2.38</v>
       </c>
       <c r="AC6" t="n">
         <v>2.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.67</v>
+        <v>1.48</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.1</v>
+        <v>2.36</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.87</v>
+        <v>1.55</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.14</v>
+        <v>1.96</v>
       </c>
       <c r="O7" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="P7" t="n">
-        <v>2.5</v>
+        <v>3.41</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.63</v>
+        <v>2.32</v>
       </c>
       <c r="R7" t="n">
-        <v>2.43</v>
+        <v>2.25</v>
       </c>
       <c r="S7" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="T7" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="U7" t="n">
-        <v>2.08</v>
+        <v>2.71</v>
       </c>
       <c r="V7" t="n">
-        <v>1.58</v>
+        <v>1.43</v>
       </c>
       <c r="W7" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.13</v>
+        <v>1.21</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.7</v>
+        <v>3.65</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.48</v>
+        <v>1.72</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.38</v>
+        <v>1.94</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.21</v>
+        <v>1.12</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.48</v>
+        <v>1.6</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.36</v>
+        <v>2.1</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.55</v>
+        <v>1.64</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,80 +1679,80 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.1</v>
+        <v>1.35</v>
       </c>
       <c r="O8" t="n">
-        <v>3.2</v>
+        <v>4.15</v>
       </c>
       <c r="P8" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="R8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AK8" t="n">
         <v>2.6</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R8" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="S8" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="U8" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>3.19</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>1.51</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,80 +1838,80 @@
         </is>
       </c>
       <c r="N9" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="O9" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R9" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="S9" t="n">
         <v>1.35</v>
       </c>
-      <c r="O9" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="P9" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="R9" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="S9" t="n">
+      <c r="T9" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ9" t="n">
         <v>1.25</v>
       </c>
-      <c r="T9" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="U9" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1.13</v>
-      </c>
       <c r="AK9" t="n">
-        <v>2.6</v>
+        <v>1.51</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>

--- a/jogos_2026-06-24.xlsx
+++ b/jogos_2026-06-24.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.98</v>
+        <v>13</v>
       </c>
       <c r="O3" t="n">
-        <v>3.18</v>
+        <v>7</v>
       </c>
       <c r="P3" t="n">
-        <v>2.8</v>
+        <v>1.13</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.65</v>
+        <v>10</v>
       </c>
       <c r="R3" t="n">
-        <v>2.3</v>
+        <v>3.3</v>
       </c>
       <c r="S3" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="T3" t="n">
-        <v>3.08</v>
+        <v>4</v>
       </c>
       <c r="U3" t="n">
-        <v>2.25</v>
+        <v>2.06</v>
       </c>
       <c r="V3" t="n">
-        <v>1.49</v>
+        <v>1.76</v>
       </c>
       <c r="W3" t="n">
-        <v>1.09</v>
+        <v>1.2</v>
       </c>
       <c r="X3" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.22</v>
+        <v>1.08</v>
       </c>
       <c r="Z3" t="n">
-        <v>4</v>
+        <v>5.75</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.7</v>
+        <v>1.39</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.01</v>
+        <v>2.59</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.74</v>
+        <v>2.04</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.38</v>
+        <v>1.68</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.15</v>
+        <v>1.33</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.5</v>
+        <v>2.05</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.3</v>
+        <v>1.64</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.22</v>
+        <v>1.05</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.52</v>
+        <v>1.01</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>13</v>
+        <v>1.98</v>
       </c>
       <c r="O4" t="n">
-        <v>7</v>
+        <v>3.18</v>
       </c>
       <c r="P4" t="n">
-        <v>1.13</v>
+        <v>2.8</v>
       </c>
       <c r="Q4" t="n">
-        <v>10</v>
+        <v>2.65</v>
       </c>
       <c r="R4" t="n">
-        <v>3.3</v>
+        <v>2.3</v>
       </c>
       <c r="S4" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="T4" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z4" t="n">
         <v>4</v>
       </c>
-      <c r="U4" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>5.75</v>
-      </c>
       <c r="AA4" t="n">
-        <v>1.39</v>
+        <v>1.7</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.59</v>
+        <v>2.01</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.04</v>
+        <v>2.74</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.68</v>
+        <v>1.38</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.33</v>
+        <v>1.15</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.05</v>
+        <v>1.5</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.64</v>
+        <v>2.3</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.05</v>
+        <v>1.22</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,80 +1679,80 @@
         </is>
       </c>
       <c r="N8" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="O8" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R8" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="S8" t="n">
         <v>1.35</v>
       </c>
-      <c r="O8" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="P8" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="R8" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="S8" t="n">
+      <c r="T8" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ8" t="n">
         <v>1.25</v>
       </c>
-      <c r="T8" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="U8" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1.13</v>
-      </c>
       <c r="AK8" t="n">
-        <v>2.6</v>
+        <v>1.51</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,80 +1838,80 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.1</v>
+        <v>1.35</v>
       </c>
       <c r="O9" t="n">
-        <v>3.2</v>
+        <v>4.15</v>
       </c>
       <c r="P9" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="R9" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AK9" t="n">
         <v>2.6</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R9" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="S9" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="U9" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>3.19</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>1.51</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>

--- a/jogos_2026-06-24.xlsx
+++ b/jogos_2026-06-24.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -693,139 +693,139 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.75</v>
+        <v>2</v>
       </c>
       <c r="O2" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="P2" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R2" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S2" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="T2" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AG2" t="n">
         <v>2.25</v>
       </c>
-      <c r="Q2" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="R2" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="S2" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="T2" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="U2" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>2.08</v>
-      </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['32', '38', '64', '89']</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['79']</t>
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.24</v>
+        <v>1.16</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.33</v>
+        <v>1.53</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN2" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO2" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AP2" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="AU2" s="3" t="n">
         <v>46197.54166666666</v>
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -880,68 +880,68 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>13</v>
+        <v>2.22</v>
       </c>
       <c r="O3" t="n">
-        <v>7</v>
+        <v>3.28</v>
       </c>
       <c r="P3" t="n">
-        <v>1.13</v>
+        <v>2.41</v>
       </c>
       <c r="Q3" t="n">
-        <v>10</v>
+        <v>2.8</v>
       </c>
       <c r="R3" t="n">
-        <v>3.3</v>
+        <v>2.13</v>
       </c>
       <c r="S3" t="n">
-        <v>1.2</v>
+        <v>1.35</v>
       </c>
       <c r="T3" t="n">
-        <v>4</v>
+        <v>2.79</v>
       </c>
       <c r="U3" t="n">
-        <v>2.06</v>
+        <v>2.71</v>
       </c>
       <c r="V3" t="n">
-        <v>1.76</v>
+        <v>1.38</v>
       </c>
       <c r="W3" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="X3" t="n">
         <v>1.01</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.08</v>
+        <v>1.25</v>
       </c>
       <c r="Z3" t="n">
-        <v>5.75</v>
+        <v>3.02</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.39</v>
+        <v>1.86</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.59</v>
+        <v>1.9</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.04</v>
+        <v>3.2</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.68</v>
+        <v>1.28</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.33</v>
+        <v>1.07</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.05</v>
+        <v>1.65</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.64</v>
+        <v>2.1</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,37 +954,37 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.05</v>
+        <v>1.25</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN3" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO3" t="n">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AP3" t="n">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="AU3" s="3" t="n">
         <v>46197.54166666666</v>
@@ -996,7 +996,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,80 +1043,80 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.98</v>
+        <v>1.84</v>
       </c>
       <c r="O4" t="n">
-        <v>3.18</v>
+        <v>3.15</v>
       </c>
       <c r="P4" t="n">
-        <v>2.8</v>
+        <v>3.15</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.65</v>
+        <v>2.54</v>
       </c>
       <c r="R4" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="S4" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ4" t="n">
         <v>1.29</v>
       </c>
-      <c r="T4" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="U4" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ4" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AK4" t="n">
-        <v>1.52</v>
+        <v>1.73</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1146,7 +1146,7 @@
         <v>0</v>
       </c>
       <c r="AU4" s="3" t="n">
-        <v>46197.54166666666</v>
+        <v>46197.58333333334</v>
       </c>
     </row>
     <row r="5">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,31 +1202,31 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.55</v>
+        <v>2.34</v>
       </c>
       <c r="O5" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P5" t="n">
-        <v>5.22</v>
+        <v>2.6</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.23</v>
+        <v>2.88</v>
       </c>
       <c r="R5" t="n">
-        <v>2.38</v>
+        <v>2.15</v>
       </c>
       <c r="S5" t="n">
         <v>1.25</v>
       </c>
       <c r="T5" t="n">
-        <v>3.6</v>
+        <v>3.14</v>
       </c>
       <c r="U5" t="n">
-        <v>2.28</v>
+        <v>2.08</v>
       </c>
       <c r="V5" t="n">
-        <v>1.49</v>
+        <v>1.58</v>
       </c>
       <c r="W5" t="n">
         <v>1.11</v>
@@ -1235,31 +1235,31 @@
         <v>1.03</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="Z5" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AC5" t="n">
         <v>2.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.43</v>
+        <v>1.55</v>
       </c>
       <c r="AE5" t="n">
         <v>1.17</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.67</v>
+        <v>1.46</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.87</v>
+        <v>1.55</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.14</v>
+        <v>1.63</v>
       </c>
       <c r="O6" t="n">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="P6" t="n">
-        <v>2.5</v>
+        <v>4.7</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.63</v>
+        <v>2.12</v>
       </c>
       <c r="R6" t="n">
-        <v>2.43</v>
+        <v>2.26</v>
       </c>
       <c r="S6" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="T6" t="n">
-        <v>3.6</v>
+        <v>3.12</v>
       </c>
       <c r="U6" t="n">
-        <v>2.08</v>
+        <v>2.46</v>
       </c>
       <c r="V6" t="n">
-        <v>1.58</v>
+        <v>1.49</v>
       </c>
       <c r="W6" t="n">
         <v>1.11</v>
       </c>
       <c r="X6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.7</v>
+        <v>3.9</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.48</v>
+        <v>1.7</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.5</v>
+        <v>2.66</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.21</v>
+        <v>1.14</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.48</v>
+        <v>1.67</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.36</v>
+        <v>2</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.55</v>
+        <v>2.2</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.96</v>
+        <v>14</v>
       </c>
       <c r="O7" t="n">
-        <v>3.5</v>
+        <v>8</v>
       </c>
       <c r="P7" t="n">
-        <v>3.41</v>
+        <v>1.15</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.32</v>
+        <v>12</v>
       </c>
       <c r="R7" t="n">
-        <v>2.25</v>
+        <v>3.3</v>
       </c>
       <c r="S7" t="n">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="T7" t="n">
-        <v>3</v>
+        <v>4.2</v>
       </c>
       <c r="U7" t="n">
-        <v>2.71</v>
+        <v>1.85</v>
       </c>
       <c r="V7" t="n">
-        <v>1.43</v>
+        <v>1.77</v>
       </c>
       <c r="W7" t="n">
-        <v>1.07</v>
+        <v>1.23</v>
       </c>
       <c r="X7" t="n">
         <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.21</v>
+        <v>1.06</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.65</v>
+        <v>7.5</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.72</v>
+        <v>1.33</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.94</v>
+        <v>3.25</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.75</v>
+        <v>1.82</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.36</v>
+        <v>1.87</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.12</v>
+        <v>1.38</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.1</v>
+        <v>1.63</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.22</v>
+        <v>1.04</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.64</v>
+        <v>1.01</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1623,7 +1623,7 @@
         <v>0</v>
       </c>
       <c r="AU7" s="3" t="n">
-        <v>46197.58333333334</v>
+        <v>46197.59375</v>
       </c>
     </row>
     <row r="8">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,65 +1679,65 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="O8" t="n">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="P8" t="n">
-        <v>2.6</v>
+        <v>5.75</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.1</v>
+        <v>1.9</v>
       </c>
       <c r="R8" t="n">
-        <v>2.09</v>
+        <v>2.4</v>
       </c>
       <c r="S8" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="T8" t="n">
-        <v>2.82</v>
+        <v>3.6</v>
       </c>
       <c r="U8" t="n">
-        <v>2.88</v>
+        <v>2.26</v>
       </c>
       <c r="V8" t="n">
-        <v>1.39</v>
+        <v>1.58</v>
       </c>
       <c r="W8" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="X8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.33</v>
+        <v>1.12</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.28</v>
+        <v>4.7</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="AB8" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AG8" t="n">
         <v>1.95</v>
       </c>
-      <c r="AC8" t="n">
-        <v>3.19</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.98</v>
-      </c>
       <c r="AH8" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.51</v>
+        <v>2.65</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="O9" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="R9" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD9" t="n">
         <v>1.35</v>
       </c>
-      <c r="O9" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="P9" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="R9" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="S9" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="T9" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="U9" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AE9" t="n">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.95</v>
+        <v>2.12</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.13</v>
+        <v>1.26</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.6</v>
+        <v>1.45</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -2006,55 +2006,55 @@
         <v>4.1</v>
       </c>
       <c r="Q10" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R10" t="n">
         <v>2.21</v>
       </c>
-      <c r="R10" t="n">
-        <v>2.19</v>
-      </c>
       <c r="S10" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="T10" t="n">
-        <v>2.81</v>
+        <v>3</v>
       </c>
       <c r="U10" t="n">
-        <v>2.51</v>
+        <v>2.59</v>
       </c>
       <c r="V10" t="n">
         <v>1.4</v>
       </c>
       <c r="W10" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X10" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AB10" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
         <v>1.2</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.01</v>
+        <v>1.91</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>

--- a/jogos_2026-06-24.xlsx
+++ b/jogos_2026-06-24.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -693,139 +693,139 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="N2" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="O2" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="P2" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R2" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="S2" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>7</v>
+      </c>
+      <c r="AN2" t="n">
         <v>4</v>
       </c>
-      <c r="H2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" t="n">
-        <v>2</v>
-      </c>
-      <c r="L2" t="n">
-        <v>1</v>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="N2" t="n">
-        <v>2</v>
-      </c>
-      <c r="O2" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="P2" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="R2" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="S2" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="T2" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="U2" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>['32', '38', '64', '89']</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>['79']</t>
-        </is>
-      </c>
-      <c r="AJ2" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>6</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>5</v>
-      </c>
       <c r="AO2" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="AP2" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.15</v>
+        <v>1.95</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.41</v>
+        <v>1.51</v>
       </c>
       <c r="AS2" t="n">
-        <v>47</v>
+        <v>80</v>
       </c>
       <c r="AT2" t="n">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="AU2" s="3" t="n">
         <v>46197.54166666666</v>
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,31 +852,31 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -884,107 +884,107 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="O3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P3" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R3" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="T3" t="n">
         <v>3.28</v>
       </c>
-      <c r="P3" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="R3" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="S3" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2.79</v>
-      </c>
       <c r="U3" t="n">
-        <v>2.71</v>
+        <v>2.4</v>
       </c>
       <c r="V3" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="W3" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.02</v>
+        <v>4.3</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.86</v>
+        <v>1.65</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.2</v>
+        <v>2.64</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.28</v>
+        <v>1.46</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['32', '38', '64', '89']</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['79']</t>
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="AK3" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AR3" t="n">
         <v>1.41</v>
       </c>
-      <c r="AL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>7</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>4</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>14</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>12</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>1.51</v>
-      </c>
       <c r="AS3" t="n">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="AT3" t="n">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="AU3" s="3" t="n">
         <v>46197.54166666666</v>
@@ -1020,13 +1020,13 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -1035,11 +1035,11 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N4" t="n">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['15']</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['60']</t>
         </is>
       </c>
       <c r="AJ4" t="n">
@@ -1122,28 +1122,28 @@
         <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN4" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO4" t="n">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP4" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="AU4" s="3" t="n">
         <v>46197.58333333334</v>
@@ -1170,16 +1170,16 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -1191,118 +1191,118 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.34</v>
+        <v>1.63</v>
       </c>
       <c r="O5" t="n">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="P5" t="n">
-        <v>2.6</v>
+        <v>4.7</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.88</v>
+        <v>2.12</v>
       </c>
       <c r="R5" t="n">
-        <v>2.15</v>
+        <v>2.26</v>
       </c>
       <c r="S5" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="T5" t="n">
-        <v>3.14</v>
+        <v>3.12</v>
       </c>
       <c r="U5" t="n">
-        <v>2.08</v>
+        <v>2.46</v>
       </c>
       <c r="V5" t="n">
-        <v>1.58</v>
+        <v>1.49</v>
       </c>
       <c r="W5" t="n">
         <v>1.11</v>
       </c>
       <c r="X5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>['48']</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>7</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ5" t="n">
         <v>1.03</v>
       </c>
-      <c r="Y5" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>0</v>
-      </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>0.92</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AU5" s="3" t="n">
         <v>46197.58333333334</v>
@@ -1329,139 +1329,139 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.63</v>
+        <v>2.34</v>
       </c>
       <c r="O6" t="n">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="P6" t="n">
-        <v>4.7</v>
+        <v>2.6</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.12</v>
+        <v>2.88</v>
       </c>
       <c r="R6" t="n">
-        <v>2.26</v>
+        <v>2.15</v>
       </c>
       <c r="S6" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="T6" t="n">
-        <v>3.12</v>
+        <v>3.14</v>
       </c>
       <c r="U6" t="n">
-        <v>2.46</v>
+        <v>2.08</v>
       </c>
       <c r="V6" t="n">
-        <v>1.49</v>
+        <v>1.58</v>
       </c>
       <c r="W6" t="n">
         <v>1.11</v>
       </c>
       <c r="X6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.9</v>
+        <v>4.7</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.66</v>
+        <v>2.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.67</v>
+        <v>1.46</v>
       </c>
       <c r="AG6" t="n">
-        <v>2</v>
+        <v>2.38</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['57', '81']</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['30']</t>
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.2</v>
+        <v>1.55</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN6" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO6" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP6" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>0.83</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="AU6" s="3" t="n">
         <v>46197.58333333334</v>
@@ -1497,26 +1497,26 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N7" t="n">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['18', '59']</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['16', '45+1', '78']</t>
         </is>
       </c>
       <c r="AJ7" t="n">
@@ -1599,28 +1599,28 @@
         <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN7" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO7" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AP7" t="n">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="AU7" s="3" t="n">
         <v>46197.59375</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.4</v>
+        <v>2.25</v>
       </c>
       <c r="O8" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="P8" t="n">
-        <v>5.75</v>
+        <v>2.6</v>
       </c>
       <c r="Q8" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="R8" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AB8" t="n">
         <v>1.9</v>
       </c>
-      <c r="R8" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="S8" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="T8" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="U8" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>2.37</v>
-      </c>
       <c r="AC8" t="n">
-        <v>2.48</v>
+        <v>3</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.55</v>
+        <v>1.35</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.95</v>
+        <v>2.12</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.11</v>
+        <v>1.26</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.65</v>
+        <v>1.45</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.25</v>
+        <v>1.4</v>
       </c>
       <c r="O9" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="P9" t="n">
-        <v>2.6</v>
+        <v>5.75</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.95</v>
+        <v>1.9</v>
       </c>
       <c r="R9" t="n">
-        <v>2.13</v>
+        <v>2.4</v>
       </c>
       <c r="S9" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T9" t="n">
-        <v>3.19</v>
+        <v>3.6</v>
       </c>
       <c r="U9" t="n">
-        <v>2.74</v>
+        <v>2.26</v>
       </c>
       <c r="V9" t="n">
-        <v>1.42</v>
+        <v>1.58</v>
       </c>
       <c r="W9" t="n">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.58</v>
+        <v>4.7</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.77</v>
+        <v>1.53</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.9</v>
+        <v>2.37</v>
       </c>
       <c r="AC9" t="n">
-        <v>3</v>
+        <v>2.48</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.35</v>
+        <v>1.55</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.12</v>
+        <v>1.95</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.26</v>
+        <v>1.11</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.45</v>
+        <v>2.65</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>

--- a/jogos_2026-06-24.xlsx
+++ b/jogos_2026-06-24.xlsx
@@ -1011,31 +1011,31 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H4" t="n">
         <v>1</v>
       </c>
       <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
         <v>1</v>
       </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1043,107 +1043,107 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.84</v>
+        <v>2.34</v>
       </c>
       <c r="O4" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="P4" t="n">
-        <v>3.15</v>
+        <v>2.6</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.54</v>
+        <v>2.88</v>
       </c>
       <c r="R4" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB4" t="n">
         <v>2.2</v>
       </c>
-      <c r="S4" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="U4" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AC4" t="n">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.31</v>
+        <v>1.55</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.6</v>
+        <v>1.46</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>['15']</t>
+          <t>['57', '81']</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>['60']</t>
+          <t>['30']</t>
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.73</v>
+        <v>1.55</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
       </c>
       <c r="AM4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AP4" t="n">
         <v>4</v>
       </c>
-      <c r="AN4" t="n">
-        <v>6</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>12</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>8</v>
-      </c>
       <c r="AQ4" t="n">
-        <v>1.47</v>
+        <v>1.17</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.44</v>
+        <v>0.83</v>
       </c>
       <c r="AS4" t="n">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="AT4" t="n">
-        <v>72</v>
+        <v>51</v>
       </c>
       <c r="AU4" s="3" t="n">
         <v>46197.58333333334</v>
@@ -1170,139 +1170,139 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G5" t="n">
         <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
         <v>1</v>
       </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
       <c r="M5" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.63</v>
+        <v>1.84</v>
       </c>
       <c r="O5" t="n">
-        <v>3.75</v>
+        <v>3.15</v>
       </c>
       <c r="P5" t="n">
-        <v>4.7</v>
+        <v>3.15</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.12</v>
+        <v>2.54</v>
       </c>
       <c r="R5" t="n">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="S5" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="T5" t="n">
-        <v>3.12</v>
+        <v>2.95</v>
       </c>
       <c r="U5" t="n">
-        <v>2.46</v>
+        <v>2.66</v>
       </c>
       <c r="V5" t="n">
-        <v>1.49</v>
+        <v>1.42</v>
       </c>
       <c r="W5" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X5" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.9</v>
+        <v>3.65</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AB5" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AG5" t="n">
         <v>2.1</v>
       </c>
-      <c r="AC5" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AD5" t="n">
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>['15']</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>['60']</t>
+        </is>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>6</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>12</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>8</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AR5" t="n">
         <v>1.44</v>
       </c>
-      <c r="AE5" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>['48']</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>3</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>4</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>7</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>5</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>0.92</v>
-      </c>
       <c r="AS5" t="n">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="AT5" t="n">
-        <v>44</v>
+        <v>72</v>
       </c>
       <c r="AU5" s="3" t="n">
         <v>46197.58333333334</v>
@@ -1329,29 +1329,29 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
         <v>1</v>
       </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K6" t="n">
-        <v>2</v>
-      </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
@@ -1361,107 +1361,107 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.34</v>
+        <v>1.63</v>
       </c>
       <c r="O6" t="n">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="P6" t="n">
-        <v>2.6</v>
+        <v>4.7</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.88</v>
+        <v>2.12</v>
       </c>
       <c r="R6" t="n">
-        <v>2.15</v>
+        <v>2.26</v>
       </c>
       <c r="S6" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="T6" t="n">
-        <v>3.14</v>
+        <v>3.12</v>
       </c>
       <c r="U6" t="n">
-        <v>2.08</v>
+        <v>2.46</v>
       </c>
       <c r="V6" t="n">
-        <v>1.58</v>
+        <v>1.49</v>
       </c>
       <c r="W6" t="n">
         <v>1.11</v>
       </c>
       <c r="X6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>['48']</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>7</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ6" t="n">
         <v>1.03</v>
       </c>
-      <c r="Y6" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>['57', '81']</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>['30']</t>
-        </is>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>5</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>3</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>8</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>4</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>1.17</v>
-      </c>
       <c r="AR6" t="n">
-        <v>0.83</v>
+        <v>0.92</v>
       </c>
       <c r="AS6" t="n">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="AT6" t="n">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="AU6" s="3" t="n">
         <v>46197.58333333334</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.25</v>
+        <v>1.4</v>
       </c>
       <c r="O8" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="P8" t="n">
-        <v>2.6</v>
+        <v>5.75</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.95</v>
+        <v>1.9</v>
       </c>
       <c r="R8" t="n">
-        <v>2.13</v>
+        <v>2.4</v>
       </c>
       <c r="S8" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T8" t="n">
-        <v>3.19</v>
+        <v>3.6</v>
       </c>
       <c r="U8" t="n">
-        <v>2.74</v>
+        <v>2.26</v>
       </c>
       <c r="V8" t="n">
-        <v>1.42</v>
+        <v>1.58</v>
       </c>
       <c r="W8" t="n">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.58</v>
+        <v>4.7</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.77</v>
+        <v>1.53</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.9</v>
+        <v>2.37</v>
       </c>
       <c r="AC8" t="n">
-        <v>3</v>
+        <v>2.48</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.35</v>
+        <v>1.55</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.12</v>
+        <v>1.95</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.26</v>
+        <v>1.11</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.45</v>
+        <v>2.65</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.4</v>
+        <v>2.25</v>
       </c>
       <c r="O9" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="P9" t="n">
-        <v>5.75</v>
+        <v>2.6</v>
       </c>
       <c r="Q9" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="R9" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AB9" t="n">
         <v>1.9</v>
       </c>
-      <c r="R9" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="S9" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="T9" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="U9" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>2.37</v>
-      </c>
       <c r="AC9" t="n">
-        <v>2.48</v>
+        <v>3</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.55</v>
+        <v>1.35</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.95</v>
+        <v>2.12</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.11</v>
+        <v>1.26</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.65</v>
+        <v>1.45</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
